--- a/Master Data R1.xlsx
+++ b/Master Data R1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\peiyi\Downloads\In Out\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\peiyi\Downloads\Study\Portfolio\In Out\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CA27ABB-2617-43D0-9070-8699F7CFD911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C571742-F207-4142-97C1-1370F55C3B9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{63164BFF-5225-4AAF-A540-1B89C6B709BD}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{63164BFF-5225-4AAF-A540-1B89C6B709BD}"/>
   </bookViews>
   <sheets>
     <sheet name="Master Data" sheetId="1" r:id="rId1"/>
@@ -19,11 +19,22 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Master Data'!$A$1:$I$190</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="955" uniqueCount="396">
   <si>
     <t>Item Desc</t>
   </si>
@@ -70,6 +81,18 @@
     <t>SKUlink</t>
   </si>
   <si>
+    <t>100028</t>
+  </si>
+  <si>
+    <t>100031</t>
+  </si>
+  <si>
+    <t>100030</t>
+  </si>
+  <si>
+    <t>100173</t>
+  </si>
+  <si>
     <t>Item 000001</t>
   </si>
   <si>
@@ -638,6 +661,561 @@
   </si>
   <si>
     <t>UOM</t>
+  </si>
+  <si>
+    <t>100001</t>
+  </si>
+  <si>
+    <t>100002</t>
+  </si>
+  <si>
+    <t>100003</t>
+  </si>
+  <si>
+    <t>100004</t>
+  </si>
+  <si>
+    <t>100005</t>
+  </si>
+  <si>
+    <t>100006</t>
+  </si>
+  <si>
+    <t>100007</t>
+  </si>
+  <si>
+    <t>100008</t>
+  </si>
+  <si>
+    <t>100009</t>
+  </si>
+  <si>
+    <t>100010</t>
+  </si>
+  <si>
+    <t>100011</t>
+  </si>
+  <si>
+    <t>100012</t>
+  </si>
+  <si>
+    <t>100013</t>
+  </si>
+  <si>
+    <t>100014</t>
+  </si>
+  <si>
+    <t>100015</t>
+  </si>
+  <si>
+    <t>100016</t>
+  </si>
+  <si>
+    <t>100017</t>
+  </si>
+  <si>
+    <t>100018</t>
+  </si>
+  <si>
+    <t>100019</t>
+  </si>
+  <si>
+    <t>100020</t>
+  </si>
+  <si>
+    <t>100021</t>
+  </si>
+  <si>
+    <t>100022</t>
+  </si>
+  <si>
+    <t>100023</t>
+  </si>
+  <si>
+    <t>100024</t>
+  </si>
+  <si>
+    <t>100025</t>
+  </si>
+  <si>
+    <t>100026</t>
+  </si>
+  <si>
+    <t>100027</t>
+  </si>
+  <si>
+    <t>100029</t>
+  </si>
+  <si>
+    <t>100032</t>
+  </si>
+  <si>
+    <t>100033</t>
+  </si>
+  <si>
+    <t>100034</t>
+  </si>
+  <si>
+    <t>100035</t>
+  </si>
+  <si>
+    <t>100036</t>
+  </si>
+  <si>
+    <t>100037</t>
+  </si>
+  <si>
+    <t>100038</t>
+  </si>
+  <si>
+    <t>100039</t>
+  </si>
+  <si>
+    <t>100040</t>
+  </si>
+  <si>
+    <t>100041</t>
+  </si>
+  <si>
+    <t>100042</t>
+  </si>
+  <si>
+    <t>100043</t>
+  </si>
+  <si>
+    <t>100044</t>
+  </si>
+  <si>
+    <t>100045</t>
+  </si>
+  <si>
+    <t>100046</t>
+  </si>
+  <si>
+    <t>100047</t>
+  </si>
+  <si>
+    <t>100048</t>
+  </si>
+  <si>
+    <t>100049</t>
+  </si>
+  <si>
+    <t>100050</t>
+  </si>
+  <si>
+    <t>100051</t>
+  </si>
+  <si>
+    <t>100052</t>
+  </si>
+  <si>
+    <t>100053</t>
+  </si>
+  <si>
+    <t>100054</t>
+  </si>
+  <si>
+    <t>100055</t>
+  </si>
+  <si>
+    <t>100056</t>
+  </si>
+  <si>
+    <t>100057</t>
+  </si>
+  <si>
+    <t>100058</t>
+  </si>
+  <si>
+    <t>100059</t>
+  </si>
+  <si>
+    <t>100060</t>
+  </si>
+  <si>
+    <t>100061</t>
+  </si>
+  <si>
+    <t>100062</t>
+  </si>
+  <si>
+    <t>100063</t>
+  </si>
+  <si>
+    <t>100064</t>
+  </si>
+  <si>
+    <t>100065</t>
+  </si>
+  <si>
+    <t>100066</t>
+  </si>
+  <si>
+    <t>100067</t>
+  </si>
+  <si>
+    <t>100068</t>
+  </si>
+  <si>
+    <t>100069</t>
+  </si>
+  <si>
+    <t>100070</t>
+  </si>
+  <si>
+    <t>100071</t>
+  </si>
+  <si>
+    <t>100072</t>
+  </si>
+  <si>
+    <t>100073</t>
+  </si>
+  <si>
+    <t>100074</t>
+  </si>
+  <si>
+    <t>100075</t>
+  </si>
+  <si>
+    <t>100076</t>
+  </si>
+  <si>
+    <t>100077</t>
+  </si>
+  <si>
+    <t>100078</t>
+  </si>
+  <si>
+    <t>100079</t>
+  </si>
+  <si>
+    <t>100080</t>
+  </si>
+  <si>
+    <t>100081</t>
+  </si>
+  <si>
+    <t>100082</t>
+  </si>
+  <si>
+    <t>100083</t>
+  </si>
+  <si>
+    <t>100084</t>
+  </si>
+  <si>
+    <t>100085</t>
+  </si>
+  <si>
+    <t>100086</t>
+  </si>
+  <si>
+    <t>100087</t>
+  </si>
+  <si>
+    <t>100088</t>
+  </si>
+  <si>
+    <t>100089</t>
+  </si>
+  <si>
+    <t>100090</t>
+  </si>
+  <si>
+    <t>100091</t>
+  </si>
+  <si>
+    <t>100092</t>
+  </si>
+  <si>
+    <t>100093</t>
+  </si>
+  <si>
+    <t>100094</t>
+  </si>
+  <si>
+    <t>100095</t>
+  </si>
+  <si>
+    <t>100096</t>
+  </si>
+  <si>
+    <t>100097</t>
+  </si>
+  <si>
+    <t>100098</t>
+  </si>
+  <si>
+    <t>100099</t>
+  </si>
+  <si>
+    <t>100100</t>
+  </si>
+  <si>
+    <t>100101</t>
+  </si>
+  <si>
+    <t>100102</t>
+  </si>
+  <si>
+    <t>100103</t>
+  </si>
+  <si>
+    <t>100104</t>
+  </si>
+  <si>
+    <t>100105</t>
+  </si>
+  <si>
+    <t>100106</t>
+  </si>
+  <si>
+    <t>100107</t>
+  </si>
+  <si>
+    <t>100108</t>
+  </si>
+  <si>
+    <t>100109</t>
+  </si>
+  <si>
+    <t>100110</t>
+  </si>
+  <si>
+    <t>100111</t>
+  </si>
+  <si>
+    <t>100112</t>
+  </si>
+  <si>
+    <t>100113</t>
+  </si>
+  <si>
+    <t>100114</t>
+  </si>
+  <si>
+    <t>100115</t>
+  </si>
+  <si>
+    <t>100116</t>
+  </si>
+  <si>
+    <t>100117</t>
+  </si>
+  <si>
+    <t>100118</t>
+  </si>
+  <si>
+    <t>100119</t>
+  </si>
+  <si>
+    <t>100120</t>
+  </si>
+  <si>
+    <t>100121</t>
+  </si>
+  <si>
+    <t>100122</t>
+  </si>
+  <si>
+    <t>100123</t>
+  </si>
+  <si>
+    <t>100124</t>
+  </si>
+  <si>
+    <t>100125</t>
+  </si>
+  <si>
+    <t>100126</t>
+  </si>
+  <si>
+    <t>100127</t>
+  </si>
+  <si>
+    <t>100128</t>
+  </si>
+  <si>
+    <t>100129</t>
+  </si>
+  <si>
+    <t>100130</t>
+  </si>
+  <si>
+    <t>100131</t>
+  </si>
+  <si>
+    <t>100132</t>
+  </si>
+  <si>
+    <t>100133</t>
+  </si>
+  <si>
+    <t>100134</t>
+  </si>
+  <si>
+    <t>100135</t>
+  </si>
+  <si>
+    <t>100136</t>
+  </si>
+  <si>
+    <t>100137</t>
+  </si>
+  <si>
+    <t>100138</t>
+  </si>
+  <si>
+    <t>100139</t>
+  </si>
+  <si>
+    <t>100140</t>
+  </si>
+  <si>
+    <t>100141</t>
+  </si>
+  <si>
+    <t>100142</t>
+  </si>
+  <si>
+    <t>100143</t>
+  </si>
+  <si>
+    <t>100144</t>
+  </si>
+  <si>
+    <t>100145</t>
+  </si>
+  <si>
+    <t>100146</t>
+  </si>
+  <si>
+    <t>100147</t>
+  </si>
+  <si>
+    <t>100148</t>
+  </si>
+  <si>
+    <t>100149</t>
+  </si>
+  <si>
+    <t>100150</t>
+  </si>
+  <si>
+    <t>100151</t>
+  </si>
+  <si>
+    <t>100152</t>
+  </si>
+  <si>
+    <t>100153</t>
+  </si>
+  <si>
+    <t>100154</t>
+  </si>
+  <si>
+    <t>100155</t>
+  </si>
+  <si>
+    <t>100156</t>
+  </si>
+  <si>
+    <t>100157</t>
+  </si>
+  <si>
+    <t>100158</t>
+  </si>
+  <si>
+    <t>100159</t>
+  </si>
+  <si>
+    <t>100160</t>
+  </si>
+  <si>
+    <t>100161</t>
+  </si>
+  <si>
+    <t>100162</t>
+  </si>
+  <si>
+    <t>100163</t>
+  </si>
+  <si>
+    <t>100164</t>
+  </si>
+  <si>
+    <t>100165</t>
+  </si>
+  <si>
+    <t>100166</t>
+  </si>
+  <si>
+    <t>100167</t>
+  </si>
+  <si>
+    <t>100168</t>
+  </si>
+  <si>
+    <t>100169</t>
+  </si>
+  <si>
+    <t>100170</t>
+  </si>
+  <si>
+    <t>100171</t>
+  </si>
+  <si>
+    <t>100172</t>
+  </si>
+  <si>
+    <t>100174</t>
+  </si>
+  <si>
+    <t>100175</t>
+  </si>
+  <si>
+    <t>100176</t>
+  </si>
+  <si>
+    <t>100177</t>
+  </si>
+  <si>
+    <t>100178</t>
+  </si>
+  <si>
+    <t>100179</t>
+  </si>
+  <si>
+    <t>100180</t>
+  </si>
+  <si>
+    <t>100181</t>
+  </si>
+  <si>
+    <t>100182</t>
+  </si>
+  <si>
+    <t>100183</t>
+  </si>
+  <si>
+    <t>100184</t>
+  </si>
+  <si>
+    <t>100185</t>
+  </si>
+  <si>
+    <t>200028</t>
+  </si>
+  <si>
+    <t>200031</t>
+  </si>
+  <si>
+    <t>200030</t>
+  </si>
+  <si>
+    <t>200173</t>
   </si>
   <si>
     <t>Category</t>
@@ -650,7 +1228,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -692,6 +1270,11 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -701,12 +1284,27 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -715,7 +1313,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -727,6 +1325,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1024,13 +1625,13 @@
         <v>13</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>205</v>
+        <v>394</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>7</v>
@@ -1044,22 +1645,22 @@
       <c r="I1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>206</v>
+      <c r="J1" s="7" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="5">
-        <v>100001</v>
-      </c>
-      <c r="B2" s="5">
-        <v>100001</v>
+      <c r="A2" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>209</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>3</v>
@@ -1074,6 +1675,7 @@
         <v>10</v>
       </c>
       <c r="I2" s="1">
+        <f t="shared" ref="I2:I6" si="0">IF(H2="", "", G2*H2)</f>
         <v>50</v>
       </c>
       <c r="J2" s="1">
@@ -1081,17 +1683,17 @@
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="5">
-        <v>100002</v>
-      </c>
-      <c r="B3" s="5">
-        <v>100002</v>
+      <c r="A3" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>210</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>3</v>
@@ -1106,6 +1708,7 @@
         <v>10</v>
       </c>
       <c r="I3" s="1">
+        <f t="shared" si="0"/>
         <v>50</v>
       </c>
       <c r="J3" s="1">
@@ -1113,17 +1716,17 @@
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="5">
-        <v>100003</v>
-      </c>
-      <c r="B4" s="5">
-        <v>100003</v>
+      <c r="A4" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>211</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>3</v>
@@ -1138,6 +1741,7 @@
         <v>10</v>
       </c>
       <c r="I4" s="1">
+        <f t="shared" si="0"/>
         <v>50</v>
       </c>
       <c r="J4" s="1">
@@ -1145,17 +1749,17 @@
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="5">
-        <v>100004</v>
-      </c>
-      <c r="B5" s="5">
-        <v>100004</v>
+      <c r="A5" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>212</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>3</v>
@@ -1170,6 +1774,7 @@
         <v>10</v>
       </c>
       <c r="I5" s="1">
+        <f t="shared" si="0"/>
         <v>50</v>
       </c>
       <c r="J5" s="1">
@@ -1177,17 +1782,17 @@
       </c>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="5">
-        <v>100005</v>
-      </c>
-      <c r="B6" s="5">
-        <v>100005</v>
+      <c r="A6" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>213</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>3</v>
@@ -1202,6 +1807,7 @@
         <v>6</v>
       </c>
       <c r="I6" s="1">
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="J6" s="1">
@@ -1209,17 +1815,17 @@
       </c>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="5">
-        <v>100006</v>
-      </c>
-      <c r="B7" s="5">
-        <v>100006</v>
+      <c r="A7" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>214</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>3</v>
@@ -1234,6 +1840,7 @@
         <v>10</v>
       </c>
       <c r="I7" s="1">
+        <f t="shared" ref="I7:I8" si="1">IF(H7="", "", G7*H7)</f>
         <v>50</v>
       </c>
       <c r="J7" s="1">
@@ -1241,17 +1848,17 @@
       </c>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="5">
-        <v>100007</v>
-      </c>
-      <c r="B8" s="5">
-        <v>100007</v>
+      <c r="A8" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>215</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>3</v>
@@ -1266,6 +1873,7 @@
         <v>9</v>
       </c>
       <c r="I8" s="1">
+        <f t="shared" si="1"/>
         <v>36</v>
       </c>
       <c r="J8" s="1">
@@ -1273,17 +1881,17 @@
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="5">
-        <v>100008</v>
-      </c>
-      <c r="B9" s="5">
-        <v>100008</v>
+      <c r="A9" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>216</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>3</v>
@@ -1298,6 +1906,7 @@
         <v>10</v>
       </c>
       <c r="I9" s="1">
+        <f t="shared" ref="I9:I22" si="2">IF(H9="", "", G9*H9)</f>
         <v>50</v>
       </c>
       <c r="J9" s="1">
@@ -1305,17 +1914,17 @@
       </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="5">
-        <v>100009</v>
-      </c>
-      <c r="B10" s="5">
-        <v>100009</v>
+      <c r="A10" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>217</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>3</v>
@@ -1330,6 +1939,7 @@
         <v>10</v>
       </c>
       <c r="I10" s="1">
+        <f t="shared" si="2"/>
         <v>50</v>
       </c>
       <c r="J10" s="1">
@@ -1337,17 +1947,17 @@
       </c>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="5">
-        <v>100010</v>
-      </c>
-      <c r="B11" s="5">
-        <v>100010</v>
+      <c r="A11" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>218</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>3</v>
@@ -1362,6 +1972,7 @@
         <v>9</v>
       </c>
       <c r="I11" s="1">
+        <f t="shared" si="2"/>
         <v>36</v>
       </c>
       <c r="J11" s="1">
@@ -1369,17 +1980,17 @@
       </c>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="5">
-        <v>100011</v>
-      </c>
-      <c r="B12" s="5">
-        <v>100011</v>
+      <c r="A12" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>219</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>3</v>
@@ -1394,6 +2005,7 @@
         <v>11</v>
       </c>
       <c r="I12" s="1">
+        <f t="shared" si="2"/>
         <v>55</v>
       </c>
       <c r="J12" s="1">
@@ -1401,17 +2013,17 @@
       </c>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="5">
-        <v>100012</v>
-      </c>
-      <c r="B13" s="5">
-        <v>100012</v>
+      <c r="A13" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>220</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>3</v>
@@ -1426,6 +2038,7 @@
         <v>21</v>
       </c>
       <c r="I13" s="1">
+        <f t="shared" si="2"/>
         <v>84</v>
       </c>
       <c r="J13" s="1">
@@ -1433,17 +2046,17 @@
       </c>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="5">
-        <v>100013</v>
-      </c>
-      <c r="B14" s="5">
-        <v>100013</v>
+      <c r="A14" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>221</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>3</v>
@@ -1458,6 +2071,7 @@
         <v>25</v>
       </c>
       <c r="I14" s="1">
+        <f t="shared" si="2"/>
         <v>175</v>
       </c>
       <c r="J14" s="1">
@@ -1465,17 +2079,17 @@
       </c>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="5">
-        <v>100014</v>
-      </c>
-      <c r="B15" s="5">
-        <v>100014</v>
+      <c r="A15" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>222</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>3</v>
@@ -1490,6 +2104,7 @@
         <v>7</v>
       </c>
       <c r="I15" s="1">
+        <f t="shared" si="2"/>
         <v>84</v>
       </c>
       <c r="J15" s="1">
@@ -1497,17 +2112,17 @@
       </c>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="5">
-        <v>100015</v>
-      </c>
-      <c r="B16" s="5">
-        <v>100015</v>
+      <c r="A16" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>223</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>3</v>
@@ -1522,6 +2137,7 @@
         <v>9</v>
       </c>
       <c r="I16" s="1">
+        <f t="shared" si="2"/>
         <v>117</v>
       </c>
       <c r="J16" s="1">
@@ -1529,17 +2145,17 @@
       </c>
     </row>
     <row r="17" spans="1:10">
-      <c r="A17" s="5">
-        <v>100016</v>
-      </c>
-      <c r="B17" s="5">
-        <v>100016</v>
+      <c r="A17" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>224</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>3</v>
@@ -1554,6 +2170,7 @@
         <v>7</v>
       </c>
       <c r="I17" s="1">
+        <f t="shared" si="2"/>
         <v>84</v>
       </c>
       <c r="J17" s="1">
@@ -1561,17 +2178,17 @@
       </c>
     </row>
     <row r="18" spans="1:10">
-      <c r="A18" s="5">
-        <v>100017</v>
-      </c>
-      <c r="B18" s="5">
-        <v>100017</v>
+      <c r="A18" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>225</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>3</v>
@@ -1586,6 +2203,7 @@
         <v>7</v>
       </c>
       <c r="I18" s="1">
+        <f t="shared" si="2"/>
         <v>84</v>
       </c>
       <c r="J18" s="1">
@@ -1593,17 +2211,17 @@
       </c>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" s="5">
-        <v>100018</v>
-      </c>
-      <c r="B19" s="5">
-        <v>100018</v>
+      <c r="A19" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>226</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>3</v>
@@ -1618,6 +2236,7 @@
         <v>9</v>
       </c>
       <c r="I19" s="1">
+        <f t="shared" si="2"/>
         <v>72</v>
       </c>
       <c r="J19" s="1">
@@ -1625,17 +2244,17 @@
       </c>
     </row>
     <row r="20" spans="1:10">
-      <c r="A20" s="5">
-        <v>100019</v>
-      </c>
-      <c r="B20" s="5">
-        <v>100019</v>
+      <c r="A20" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>227</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>3</v>
@@ -1650,6 +2269,7 @@
         <v>9</v>
       </c>
       <c r="I20" s="1">
+        <f t="shared" si="2"/>
         <v>72</v>
       </c>
       <c r="J20" s="1">
@@ -1657,17 +2277,17 @@
       </c>
     </row>
     <row r="21" spans="1:10">
-      <c r="A21" s="5">
-        <v>100020</v>
-      </c>
-      <c r="B21" s="5">
-        <v>100020</v>
+      <c r="A21" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>228</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>3</v>
@@ -1682,6 +2302,7 @@
         <v>9</v>
       </c>
       <c r="I21" s="1">
+        <f t="shared" si="2"/>
         <v>72</v>
       </c>
       <c r="J21" s="1">
@@ -1689,17 +2310,17 @@
       </c>
     </row>
     <row r="22" spans="1:10">
-      <c r="A22" s="5">
-        <v>100021</v>
-      </c>
-      <c r="B22" s="5">
-        <v>100021</v>
+      <c r="A22" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>229</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>3</v>
@@ -1714,6 +2335,7 @@
         <v>9</v>
       </c>
       <c r="I22" s="1">
+        <f t="shared" si="2"/>
         <v>72</v>
       </c>
       <c r="J22" s="1">
@@ -1721,17 +2343,17 @@
       </c>
     </row>
     <row r="23" spans="1:10">
-      <c r="A23" s="5">
-        <v>100022</v>
-      </c>
-      <c r="B23" s="5">
-        <v>100022</v>
+      <c r="A23" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>230</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>3</v>
@@ -1746,6 +2368,7 @@
         <v>17</v>
       </c>
       <c r="I23" s="1">
+        <f t="shared" ref="I23" si="3">IF(H23="", "", G23*H23)</f>
         <v>102</v>
       </c>
       <c r="J23" s="1">
@@ -1753,17 +2376,17 @@
       </c>
     </row>
     <row r="24" spans="1:10">
-      <c r="A24" s="5">
-        <v>100023</v>
-      </c>
-      <c r="B24" s="5">
-        <v>100023</v>
+      <c r="A24" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>231</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>3</v>
@@ -1778,6 +2401,7 @@
         <v>11</v>
       </c>
       <c r="I24" s="1">
+        <f t="shared" ref="I24" si="4">IF(H24="", "", G24*H24)</f>
         <v>55</v>
       </c>
       <c r="J24" s="1">
@@ -1785,17 +2409,17 @@
       </c>
     </row>
     <row r="25" spans="1:10">
-      <c r="A25" s="5">
-        <v>100024</v>
-      </c>
-      <c r="B25" s="5">
-        <v>100024</v>
+      <c r="A25" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>232</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>3</v>
@@ -1810,6 +2434,7 @@
         <v>10</v>
       </c>
       <c r="I25" s="1">
+        <f t="shared" ref="I25:I27" si="5">IF(H25="", "", G25*H25)</f>
         <v>50</v>
       </c>
       <c r="J25" s="1">
@@ -1817,17 +2442,17 @@
       </c>
     </row>
     <row r="26" spans="1:10">
-      <c r="A26" s="5">
-        <v>100025</v>
-      </c>
-      <c r="B26" s="5">
-        <v>100025</v>
+      <c r="A26" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>233</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>3</v>
@@ -1842,6 +2467,7 @@
         <v>10</v>
       </c>
       <c r="I26" s="1">
+        <f t="shared" si="5"/>
         <v>50</v>
       </c>
       <c r="J26" s="1">
@@ -1849,17 +2475,17 @@
       </c>
     </row>
     <row r="27" spans="1:10">
-      <c r="A27" s="5">
-        <v>100026</v>
-      </c>
-      <c r="B27" s="5">
-        <v>100026</v>
+      <c r="A27" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>234</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>3</v>
@@ -1874,6 +2500,7 @@
         <v>9</v>
       </c>
       <c r="I27" s="1">
+        <f t="shared" si="5"/>
         <v>36</v>
       </c>
       <c r="J27" s="1">
@@ -1881,17 +2508,17 @@
       </c>
     </row>
     <row r="28" spans="1:10">
-      <c r="A28" s="5">
-        <v>100027</v>
-      </c>
-      <c r="B28" s="5">
-        <v>100027</v>
+      <c r="A28" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>235</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>3</v>
@@ -1906,6 +2533,7 @@
         <v>11</v>
       </c>
       <c r="I28" s="1">
+        <f t="shared" ref="I28:I35" si="6">IF(H28="", "", G28*H28)</f>
         <v>55</v>
       </c>
       <c r="J28" s="1">
@@ -1913,17 +2541,17 @@
       </c>
     </row>
     <row r="29" spans="1:10">
-      <c r="A29" s="5">
-        <v>100028</v>
-      </c>
-      <c r="B29" s="5">
-        <v>100028</v>
+      <c r="A29" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>15</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>3</v>
@@ -1938,6 +2566,7 @@
         <v>11</v>
       </c>
       <c r="I29" s="1">
+        <f t="shared" si="6"/>
         <v>55</v>
       </c>
       <c r="J29" s="1">
@@ -1945,17 +2574,17 @@
       </c>
     </row>
     <row r="30" spans="1:10">
-      <c r="A30" s="5">
-        <v>100028</v>
-      </c>
-      <c r="B30" s="5">
-        <v>200028</v>
+      <c r="A30" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>390</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>4</v>
@@ -1970,6 +2599,7 @@
         <v>11</v>
       </c>
       <c r="I30" s="1">
+        <f t="shared" si="6"/>
         <v>55</v>
       </c>
       <c r="J30" s="1">
@@ -1977,17 +2607,17 @@
       </c>
     </row>
     <row r="31" spans="1:10">
-      <c r="A31" s="5">
-        <v>100029</v>
-      </c>
-      <c r="B31" s="5">
-        <v>100029</v>
+      <c r="A31" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>236</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>3</v>
@@ -2002,6 +2632,7 @@
         <v>21</v>
       </c>
       <c r="I31" s="1">
+        <f t="shared" si="6"/>
         <v>84</v>
       </c>
       <c r="J31" s="1">
@@ -2009,17 +2640,17 @@
       </c>
     </row>
     <row r="32" spans="1:10">
-      <c r="A32" s="5">
-        <v>100030</v>
-      </c>
-      <c r="B32" s="5">
-        <v>100030</v>
+      <c r="A32" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>3</v>
@@ -2034,6 +2665,7 @@
         <v>11</v>
       </c>
       <c r="I32" s="1">
+        <f t="shared" si="6"/>
         <v>55</v>
       </c>
       <c r="J32" s="1">
@@ -2041,17 +2673,17 @@
       </c>
     </row>
     <row r="33" spans="1:10">
-      <c r="A33" s="5">
-        <v>100030</v>
-      </c>
-      <c r="B33" s="5">
-        <v>200030</v>
+      <c r="A33" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>392</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>4</v>
@@ -2066,6 +2698,7 @@
         <v>11</v>
       </c>
       <c r="I33" s="1">
+        <f t="shared" si="6"/>
         <v>55</v>
       </c>
       <c r="J33" s="1">
@@ -2073,17 +2706,17 @@
       </c>
     </row>
     <row r="34" spans="1:10">
-      <c r="A34" s="5">
-        <v>100031</v>
-      </c>
-      <c r="B34" s="5">
-        <v>100031</v>
+      <c r="A34" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>3</v>
@@ -2098,6 +2731,7 @@
         <v>11</v>
       </c>
       <c r="I34" s="1">
+        <f t="shared" si="6"/>
         <v>55</v>
       </c>
       <c r="J34" s="1">
@@ -2105,17 +2739,17 @@
       </c>
     </row>
     <row r="35" spans="1:10">
-      <c r="A35" s="5">
-        <v>100031</v>
-      </c>
-      <c r="B35" s="5">
-        <v>200031</v>
+      <c r="A35" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>391</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>4</v>
@@ -2130,6 +2764,7 @@
         <v>11</v>
       </c>
       <c r="I35" s="1">
+        <f t="shared" si="6"/>
         <v>55</v>
       </c>
       <c r="J35" s="1">
@@ -2137,17 +2772,17 @@
       </c>
     </row>
     <row r="36" spans="1:10">
-      <c r="A36" s="5">
-        <v>100032</v>
-      </c>
-      <c r="B36" s="5">
-        <v>100032</v>
+      <c r="A36" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>237</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>3</v>
@@ -2162,6 +2797,7 @@
         <v>9</v>
       </c>
       <c r="I36" s="1">
+        <f t="shared" ref="I36:I38" si="7">IF(H36="", "", G36*H36)</f>
         <v>36</v>
       </c>
       <c r="J36" s="1">
@@ -2169,17 +2805,17 @@
       </c>
     </row>
     <row r="37" spans="1:10">
-      <c r="A37" s="5">
-        <v>100033</v>
-      </c>
-      <c r="B37" s="5">
-        <v>100033</v>
+      <c r="A37" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>238</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>3</v>
@@ -2194,6 +2830,7 @@
         <v>9</v>
       </c>
       <c r="I37" s="1">
+        <f t="shared" si="7"/>
         <v>36</v>
       </c>
       <c r="J37" s="1">
@@ -2201,17 +2838,17 @@
       </c>
     </row>
     <row r="38" spans="1:10">
-      <c r="A38" s="5">
-        <v>100034</v>
-      </c>
-      <c r="B38" s="5">
-        <v>100034</v>
+      <c r="A38" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>239</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>3</v>
@@ -2226,6 +2863,7 @@
         <v>9</v>
       </c>
       <c r="I38" s="1">
+        <f t="shared" si="7"/>
         <v>36</v>
       </c>
       <c r="J38" s="1">
@@ -2233,17 +2871,17 @@
       </c>
     </row>
     <row r="39" spans="1:10">
-      <c r="A39" s="5">
-        <v>100035</v>
-      </c>
-      <c r="B39" s="5">
-        <v>100035</v>
+      <c r="A39" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>240</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>3</v>
@@ -2258,6 +2896,7 @@
         <v>11</v>
       </c>
       <c r="I39" s="1">
+        <f t="shared" ref="I39:I46" si="8">IF(H39="", "", G39*H39)</f>
         <v>55</v>
       </c>
       <c r="J39" s="1">
@@ -2265,17 +2904,17 @@
       </c>
     </row>
     <row r="40" spans="1:10">
-      <c r="A40" s="5">
-        <v>100036</v>
-      </c>
-      <c r="B40" s="5">
-        <v>100036</v>
+      <c r="A40" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>241</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>3</v>
@@ -2290,24 +2929,25 @@
         <v>11</v>
       </c>
       <c r="I40" s="1">
+        <f t="shared" si="8"/>
         <v>55</v>
       </c>
       <c r="J40" s="1">
-        <v>2.39</v>
+        <v>2.3899999999999997</v>
       </c>
     </row>
     <row r="41" spans="1:10">
-      <c r="A41" s="5">
-        <v>100037</v>
-      </c>
-      <c r="B41" s="5">
-        <v>100037</v>
+      <c r="A41" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>242</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>3</v>
@@ -2322,6 +2962,7 @@
         <v>5</v>
       </c>
       <c r="I41" s="1">
+        <f t="shared" si="8"/>
         <v>45</v>
       </c>
       <c r="J41" s="1">
@@ -2329,17 +2970,17 @@
       </c>
     </row>
     <row r="42" spans="1:10">
-      <c r="A42" s="5">
-        <v>100038</v>
-      </c>
-      <c r="B42" s="5">
-        <v>100038</v>
+      <c r="A42" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>243</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>3</v>
@@ -2354,6 +2995,7 @@
         <v>5</v>
       </c>
       <c r="I42" s="1">
+        <f t="shared" si="8"/>
         <v>45</v>
       </c>
       <c r="J42" s="1">
@@ -2361,17 +3003,17 @@
       </c>
     </row>
     <row r="43" spans="1:10">
-      <c r="A43" s="5">
-        <v>100039</v>
-      </c>
-      <c r="B43" s="5">
-        <v>100039</v>
+      <c r="A43" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>244</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>3</v>
@@ -2386,6 +3028,7 @@
         <v>5</v>
       </c>
       <c r="I43" s="1">
+        <f t="shared" si="8"/>
         <v>45</v>
       </c>
       <c r="J43" s="1">
@@ -2393,17 +3036,17 @@
       </c>
     </row>
     <row r="44" spans="1:10">
-      <c r="A44" s="5">
-        <v>100040</v>
-      </c>
-      <c r="B44" s="5">
-        <v>100040</v>
+      <c r="A44" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>245</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>3</v>
@@ -2418,6 +3061,7 @@
         <v>5</v>
       </c>
       <c r="I44" s="1">
+        <f t="shared" si="8"/>
         <v>45</v>
       </c>
       <c r="J44" s="1">
@@ -2425,17 +3069,17 @@
       </c>
     </row>
     <row r="45" spans="1:10">
-      <c r="A45" s="5">
-        <v>100041</v>
-      </c>
-      <c r="B45" s="5">
-        <v>100041</v>
+      <c r="A45" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>246</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>3</v>
@@ -2450,6 +3094,7 @@
         <v>5</v>
       </c>
       <c r="I45" s="1">
+        <f t="shared" si="8"/>
         <v>45</v>
       </c>
       <c r="J45" s="1">
@@ -2457,17 +3102,17 @@
       </c>
     </row>
     <row r="46" spans="1:10">
-      <c r="A46" s="5">
-        <v>100042</v>
-      </c>
-      <c r="B46" s="5">
-        <v>100042</v>
+      <c r="A46" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>247</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>3</v>
@@ -2482,6 +3127,7 @@
         <v>5</v>
       </c>
       <c r="I46" s="1">
+        <f t="shared" si="8"/>
         <v>45</v>
       </c>
       <c r="J46" s="1">
@@ -2489,17 +3135,17 @@
       </c>
     </row>
     <row r="47" spans="1:10">
-      <c r="A47" s="5">
-        <v>100043</v>
-      </c>
-      <c r="B47" s="5">
-        <v>100043</v>
+      <c r="A47" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>248</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>3</v>
@@ -2514,6 +3160,7 @@
         <v>11</v>
       </c>
       <c r="I47" s="1">
+        <f t="shared" ref="I47:I49" si="9">IF(H47="", "", G47*H47)</f>
         <v>55</v>
       </c>
       <c r="J47" s="1">
@@ -2521,17 +3168,17 @@
       </c>
     </row>
     <row r="48" spans="1:10">
-      <c r="A48" s="5">
-        <v>100044</v>
-      </c>
-      <c r="B48" s="5">
-        <v>100044</v>
+      <c r="A48" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>249</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>3</v>
@@ -2546,6 +3193,7 @@
         <v>11</v>
       </c>
       <c r="I48" s="1">
+        <f t="shared" si="9"/>
         <v>55</v>
       </c>
       <c r="J48" s="1">
@@ -2553,17 +3201,17 @@
       </c>
     </row>
     <row r="49" spans="1:10">
-      <c r="A49" s="5">
-        <v>100045</v>
-      </c>
-      <c r="B49" s="5">
-        <v>100045</v>
+      <c r="A49" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>250</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>3</v>
@@ -2578,6 +3226,7 @@
         <v>11</v>
       </c>
       <c r="I49" s="1">
+        <f t="shared" si="9"/>
         <v>55</v>
       </c>
       <c r="J49" s="1">
@@ -2585,17 +3234,17 @@
       </c>
     </row>
     <row r="50" spans="1:10">
-      <c r="A50" s="5">
-        <v>100046</v>
-      </c>
-      <c r="B50" s="5">
-        <v>100046</v>
+      <c r="A50" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>251</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>3</v>
@@ -2610,6 +3259,7 @@
         <v>28</v>
       </c>
       <c r="I50" s="1">
+        <f t="shared" ref="I50:I76" si="10">IF(H50="", "", G50*H50)</f>
         <v>140</v>
       </c>
       <c r="J50" s="1">
@@ -2617,17 +3267,17 @@
       </c>
     </row>
     <row r="51" spans="1:10">
-      <c r="A51" s="5">
-        <v>100047</v>
-      </c>
-      <c r="B51" s="5">
-        <v>100047</v>
+      <c r="A51" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>252</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>3</v>
@@ -2642,6 +3292,7 @@
         <v>15</v>
       </c>
       <c r="I51" s="1">
+        <f t="shared" si="10"/>
         <v>75</v>
       </c>
       <c r="J51" s="1">
@@ -2649,17 +3300,17 @@
       </c>
     </row>
     <row r="52" spans="1:10">
-      <c r="A52" s="5">
-        <v>100048</v>
-      </c>
-      <c r="B52" s="5">
-        <v>100048</v>
+      <c r="A52" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>253</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>3</v>
@@ -2674,6 +3325,7 @@
         <v>18</v>
       </c>
       <c r="I52" s="1">
+        <f t="shared" si="10"/>
         <v>54</v>
       </c>
       <c r="J52" s="1">
@@ -2681,17 +3333,17 @@
       </c>
     </row>
     <row r="53" spans="1:10">
-      <c r="A53" s="5">
-        <v>100049</v>
-      </c>
-      <c r="B53" s="5">
-        <v>100049</v>
+      <c r="A53" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>254</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>3</v>
@@ -2706,6 +3358,7 @@
         <v>15</v>
       </c>
       <c r="I53" s="1">
+        <f t="shared" si="10"/>
         <v>75</v>
       </c>
       <c r="J53" s="1">
@@ -2713,17 +3366,17 @@
       </c>
     </row>
     <row r="54" spans="1:10">
-      <c r="A54" s="5">
-        <v>100050</v>
-      </c>
-      <c r="B54" s="5">
-        <v>100050</v>
+      <c r="A54" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>255</v>
       </c>
       <c r="C54" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>3</v>
@@ -2738,6 +3391,7 @@
         <v>15</v>
       </c>
       <c r="I54" s="1">
+        <f t="shared" si="10"/>
         <v>75</v>
       </c>
       <c r="J54" s="1">
@@ -2745,17 +3399,17 @@
       </c>
     </row>
     <row r="55" spans="1:10">
-      <c r="A55" s="5">
-        <v>100051</v>
-      </c>
-      <c r="B55" s="5">
-        <v>100051</v>
+      <c r="A55" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>256</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>3</v>
@@ -2770,6 +3424,7 @@
         <v>22</v>
       </c>
       <c r="I55" s="1">
+        <f t="shared" si="10"/>
         <v>88</v>
       </c>
       <c r="J55" s="1">
@@ -2777,17 +3432,17 @@
       </c>
     </row>
     <row r="56" spans="1:10">
-      <c r="A56" s="5">
-        <v>100052</v>
-      </c>
-      <c r="B56" s="5">
-        <v>100052</v>
+      <c r="A56" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>257</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>3</v>
@@ -2802,6 +3457,7 @@
         <v>22</v>
       </c>
       <c r="I56" s="1">
+        <f t="shared" si="10"/>
         <v>88</v>
       </c>
       <c r="J56" s="1">
@@ -2809,17 +3465,17 @@
       </c>
     </row>
     <row r="57" spans="1:10">
-      <c r="A57" s="5">
-        <v>100053</v>
-      </c>
-      <c r="B57" s="5">
-        <v>100053</v>
+      <c r="A57" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>258</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>3</v>
@@ -2834,6 +3490,7 @@
         <v>16</v>
       </c>
       <c r="I57" s="1">
+        <f t="shared" si="10"/>
         <v>64</v>
       </c>
       <c r="J57" s="1">
@@ -2841,17 +3498,17 @@
       </c>
     </row>
     <row r="58" spans="1:10">
-      <c r="A58" s="5">
-        <v>100054</v>
-      </c>
-      <c r="B58" s="5">
-        <v>100054</v>
+      <c r="A58" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>259</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>3</v>
@@ -2866,6 +3523,7 @@
         <v>28</v>
       </c>
       <c r="I58" s="1">
+        <f t="shared" si="10"/>
         <v>140</v>
       </c>
       <c r="J58" s="1">
@@ -2873,17 +3531,17 @@
       </c>
     </row>
     <row r="59" spans="1:10">
-      <c r="A59" s="5">
-        <v>100055</v>
-      </c>
-      <c r="B59" s="5">
-        <v>100055</v>
+      <c r="A59" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>260</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>3</v>
@@ -2898,6 +3556,7 @@
         <v>9</v>
       </c>
       <c r="I59" s="1">
+        <f t="shared" si="10"/>
         <v>54</v>
       </c>
       <c r="J59" s="1">
@@ -2905,17 +3564,17 @@
       </c>
     </row>
     <row r="60" spans="1:10">
-      <c r="A60" s="5">
-        <v>100056</v>
-      </c>
-      <c r="B60" s="5">
-        <v>100056</v>
+      <c r="A60" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>261</v>
       </c>
       <c r="C60" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>3</v>
@@ -2930,6 +3589,7 @@
         <v>12</v>
       </c>
       <c r="I60" s="1">
+        <f t="shared" si="10"/>
         <v>60</v>
       </c>
       <c r="J60" s="1">
@@ -2937,17 +3597,17 @@
       </c>
     </row>
     <row r="61" spans="1:10">
-      <c r="A61" s="5">
-        <v>100057</v>
-      </c>
-      <c r="B61" s="5">
-        <v>100057</v>
+      <c r="A61" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>262</v>
       </c>
       <c r="C61" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>3</v>
@@ -2962,6 +3622,7 @@
         <v>15</v>
       </c>
       <c r="I61" s="1">
+        <f t="shared" si="10"/>
         <v>120</v>
       </c>
       <c r="J61" s="1">
@@ -2969,17 +3630,17 @@
       </c>
     </row>
     <row r="62" spans="1:10">
-      <c r="A62" s="5">
-        <v>100058</v>
-      </c>
-      <c r="B62" s="5">
-        <v>100058</v>
+      <c r="A62" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>263</v>
       </c>
       <c r="C62" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>3</v>
@@ -2994,6 +3655,7 @@
         <v>16</v>
       </c>
       <c r="I62" s="1">
+        <f t="shared" si="10"/>
         <v>80</v>
       </c>
       <c r="J62" s="1">
@@ -3001,17 +3663,17 @@
       </c>
     </row>
     <row r="63" spans="1:10">
-      <c r="A63" s="5">
-        <v>100059</v>
-      </c>
-      <c r="B63" s="5">
-        <v>100059</v>
+      <c r="A63" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>264</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>3</v>
@@ -3026,6 +3688,7 @@
         <v>22</v>
       </c>
       <c r="I63" s="1">
+        <f t="shared" si="10"/>
         <v>88</v>
       </c>
       <c r="J63" s="1">
@@ -3033,17 +3696,17 @@
       </c>
     </row>
     <row r="64" spans="1:10">
-      <c r="A64" s="5">
-        <v>100060</v>
-      </c>
-      <c r="B64" s="5">
-        <v>100060</v>
+      <c r="A64" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>265</v>
       </c>
       <c r="C64" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>3</v>
@@ -3058,6 +3721,7 @@
         <v>28</v>
       </c>
       <c r="I64" s="1">
+        <f t="shared" si="10"/>
         <v>140</v>
       </c>
       <c r="J64" s="1">
@@ -3065,17 +3729,17 @@
       </c>
     </row>
     <row r="65" spans="1:10">
-      <c r="A65" s="5">
-        <v>100061</v>
-      </c>
-      <c r="B65" s="5">
-        <v>100061</v>
+      <c r="A65" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>266</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>3</v>
@@ -3090,6 +3754,7 @@
         <v>8</v>
       </c>
       <c r="I65" s="1">
+        <f t="shared" si="10"/>
         <v>48</v>
       </c>
       <c r="J65" s="1">
@@ -3097,17 +3762,17 @@
       </c>
     </row>
     <row r="66" spans="1:10">
-      <c r="A66" s="5">
-        <v>100062</v>
-      </c>
-      <c r="B66" s="5">
-        <v>100062</v>
+      <c r="A66" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>267</v>
       </c>
       <c r="C66" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>3</v>
@@ -3122,6 +3787,7 @@
         <v>22</v>
       </c>
       <c r="I66" s="1">
+        <f t="shared" si="10"/>
         <v>88</v>
       </c>
       <c r="J66" s="1">
@@ -3129,17 +3795,17 @@
       </c>
     </row>
     <row r="67" spans="1:10">
-      <c r="A67" s="5">
-        <v>100063</v>
-      </c>
-      <c r="B67" s="5">
-        <v>100063</v>
+      <c r="A67" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>268</v>
       </c>
       <c r="C67" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>3</v>
@@ -3154,6 +3820,7 @@
         <v>7</v>
       </c>
       <c r="I67" s="1">
+        <f t="shared" si="10"/>
         <v>56</v>
       </c>
       <c r="J67" s="1">
@@ -3161,17 +3828,17 @@
       </c>
     </row>
     <row r="68" spans="1:10">
-      <c r="A68" s="5">
-        <v>100064</v>
-      </c>
-      <c r="B68" s="5">
-        <v>100064</v>
+      <c r="A68" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>269</v>
       </c>
       <c r="C68" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>3</v>
@@ -3186,6 +3853,7 @@
         <v>15</v>
       </c>
       <c r="I68" s="1">
+        <f t="shared" si="10"/>
         <v>75</v>
       </c>
       <c r="J68" s="1">
@@ -3193,17 +3861,17 @@
       </c>
     </row>
     <row r="69" spans="1:10">
-      <c r="A69" s="5">
-        <v>100065</v>
-      </c>
-      <c r="B69" s="5">
-        <v>100065</v>
+      <c r="A69" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>270</v>
       </c>
       <c r="C69" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>3</v>
@@ -3218,6 +3886,7 @@
         <v>12</v>
       </c>
       <c r="I69" s="1">
+        <f t="shared" si="10"/>
         <v>60</v>
       </c>
       <c r="J69" s="1">
@@ -3225,17 +3894,17 @@
       </c>
     </row>
     <row r="70" spans="1:10">
-      <c r="A70" s="5">
-        <v>100066</v>
-      </c>
-      <c r="B70" s="5">
-        <v>100066</v>
+      <c r="A70" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>271</v>
       </c>
       <c r="C70" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>3</v>
@@ -3250,6 +3919,7 @@
         <v>22</v>
       </c>
       <c r="I70" s="1">
+        <f t="shared" si="10"/>
         <v>88</v>
       </c>
       <c r="J70" s="1">
@@ -3257,17 +3927,17 @@
       </c>
     </row>
     <row r="71" spans="1:10">
-      <c r="A71" s="5">
-        <v>100067</v>
-      </c>
-      <c r="B71" s="5">
-        <v>100067</v>
+      <c r="A71" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>272</v>
       </c>
       <c r="C71" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>3</v>
@@ -3282,6 +3952,7 @@
         <v>15</v>
       </c>
       <c r="I71" s="1">
+        <f t="shared" si="10"/>
         <v>120</v>
       </c>
       <c r="J71" s="1">
@@ -3289,17 +3960,17 @@
       </c>
     </row>
     <row r="72" spans="1:10">
-      <c r="A72" s="5">
-        <v>100068</v>
-      </c>
-      <c r="B72" s="5">
-        <v>100068</v>
+      <c r="A72" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>273</v>
       </c>
       <c r="C72" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>3</v>
@@ -3314,6 +3985,7 @@
         <v>5</v>
       </c>
       <c r="I72" s="1">
+        <f t="shared" si="10"/>
         <v>50</v>
       </c>
       <c r="J72" s="1">
@@ -3321,17 +3993,17 @@
       </c>
     </row>
     <row r="73" spans="1:10">
-      <c r="A73" s="5">
-        <v>100069</v>
-      </c>
-      <c r="B73" s="5">
-        <v>100069</v>
+      <c r="A73" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>274</v>
       </c>
       <c r="C73" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>3</v>
@@ -3346,6 +4018,7 @@
         <v>10</v>
       </c>
       <c r="I73" s="1">
+        <f t="shared" si="10"/>
         <v>50</v>
       </c>
       <c r="J73" s="1">
@@ -3353,17 +4026,17 @@
       </c>
     </row>
     <row r="74" spans="1:10">
-      <c r="A74" s="5">
-        <v>100070</v>
-      </c>
-      <c r="B74" s="5">
-        <v>100070</v>
+      <c r="A74" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>275</v>
       </c>
       <c r="C74" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>3</v>
@@ -3378,6 +4051,7 @@
         <v>10</v>
       </c>
       <c r="I74" s="1">
+        <f t="shared" si="10"/>
         <v>50</v>
       </c>
       <c r="J74" s="1">
@@ -3385,17 +4059,17 @@
       </c>
     </row>
     <row r="75" spans="1:10">
-      <c r="A75" s="5">
-        <v>100071</v>
-      </c>
-      <c r="B75" s="5">
-        <v>100071</v>
+      <c r="A75" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>276</v>
       </c>
       <c r="C75" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>3</v>
@@ -3410,6 +4084,7 @@
         <v>9</v>
       </c>
       <c r="I75" s="1">
+        <f t="shared" si="10"/>
         <v>36</v>
       </c>
       <c r="J75" s="1">
@@ -3417,17 +4092,17 @@
       </c>
     </row>
     <row r="76" spans="1:10">
-      <c r="A76" s="5">
-        <v>100072</v>
-      </c>
-      <c r="B76" s="5">
-        <v>100072</v>
+      <c r="A76" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>277</v>
       </c>
       <c r="C76" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>3</v>
@@ -3442,6 +4117,7 @@
         <v>9</v>
       </c>
       <c r="I76" s="1">
+        <f t="shared" si="10"/>
         <v>36</v>
       </c>
       <c r="J76" s="1">
@@ -3449,17 +4125,17 @@
       </c>
     </row>
     <row r="77" spans="1:10">
-      <c r="A77" s="5">
-        <v>100073</v>
-      </c>
-      <c r="B77" s="5">
-        <v>100073</v>
+      <c r="A77" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>278</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>3</v>
@@ -3474,6 +4150,7 @@
         <v>10</v>
       </c>
       <c r="I77" s="1">
+        <f t="shared" ref="I77:I86" si="11">IF(H77="", "", G77*H77)</f>
         <v>40</v>
       </c>
       <c r="J77" s="1">
@@ -3481,17 +4158,17 @@
       </c>
     </row>
     <row r="78" spans="1:10">
-      <c r="A78" s="5">
-        <v>100074</v>
-      </c>
-      <c r="B78" s="5">
-        <v>100074</v>
+      <c r="A78" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>279</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>3</v>
@@ -3506,6 +4183,7 @@
         <v>10</v>
       </c>
       <c r="I78" s="1">
+        <f t="shared" si="11"/>
         <v>40</v>
       </c>
       <c r="J78" s="1">
@@ -3513,17 +4191,17 @@
       </c>
     </row>
     <row r="79" spans="1:10">
-      <c r="A79" s="5">
-        <v>100075</v>
-      </c>
-      <c r="B79" s="5">
-        <v>100075</v>
+      <c r="A79" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>280</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>3</v>
@@ -3538,6 +4216,7 @@
         <v>10</v>
       </c>
       <c r="I79" s="1">
+        <f t="shared" si="11"/>
         <v>40</v>
       </c>
       <c r="J79" s="1">
@@ -3545,17 +4224,17 @@
       </c>
     </row>
     <row r="80" spans="1:10">
-      <c r="A80" s="5">
-        <v>100076</v>
-      </c>
-      <c r="B80" s="5">
-        <v>100076</v>
+      <c r="A80" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>281</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>3</v>
@@ -3570,6 +4249,7 @@
         <v>6</v>
       </c>
       <c r="I80" s="1">
+        <f t="shared" si="11"/>
         <v>36</v>
       </c>
       <c r="J80" s="1">
@@ -3577,17 +4257,17 @@
       </c>
     </row>
     <row r="81" spans="1:10">
-      <c r="A81" s="5">
-        <v>100077</v>
-      </c>
-      <c r="B81" s="5">
-        <v>100077</v>
+      <c r="A81" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>282</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>3</v>
@@ -3602,6 +4282,7 @@
         <v>6</v>
       </c>
       <c r="I81" s="1">
+        <f t="shared" si="11"/>
         <v>36</v>
       </c>
       <c r="J81" s="1">
@@ -3609,17 +4290,17 @@
       </c>
     </row>
     <row r="82" spans="1:10">
-      <c r="A82" s="5">
-        <v>100078</v>
-      </c>
-      <c r="B82" s="5">
-        <v>100078</v>
+      <c r="A82" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>283</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>3</v>
@@ -3634,6 +4315,7 @@
         <v>7</v>
       </c>
       <c r="I82" s="1">
+        <f t="shared" si="11"/>
         <v>28</v>
       </c>
       <c r="J82" s="1">
@@ -3641,17 +4323,17 @@
       </c>
     </row>
     <row r="83" spans="1:10">
-      <c r="A83" s="5">
-        <v>100079</v>
-      </c>
-      <c r="B83" s="5">
-        <v>100079</v>
+      <c r="A83" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="B83" s="5" t="s">
+        <v>284</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>3</v>
@@ -3666,6 +4348,7 @@
         <v>7</v>
       </c>
       <c r="I83" s="1">
+        <f t="shared" si="11"/>
         <v>28</v>
       </c>
       <c r="J83" s="1">
@@ -3673,17 +4356,17 @@
       </c>
     </row>
     <row r="84" spans="1:10">
-      <c r="A84" s="5">
-        <v>100080</v>
-      </c>
-      <c r="B84" s="5">
-        <v>100080</v>
+      <c r="A84" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="B84" s="5" t="s">
+        <v>285</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>3</v>
@@ -3698,6 +4381,7 @@
         <v>10</v>
       </c>
       <c r="I84" s="1">
+        <f t="shared" si="11"/>
         <v>40</v>
       </c>
       <c r="J84" s="1">
@@ -3705,17 +4389,17 @@
       </c>
     </row>
     <row r="85" spans="1:10">
-      <c r="A85" s="5">
-        <v>100081</v>
-      </c>
-      <c r="B85" s="5">
-        <v>100081</v>
+      <c r="A85" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>286</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>3</v>
@@ -3730,6 +4414,7 @@
         <v>6</v>
       </c>
       <c r="I85" s="1">
+        <f t="shared" si="11"/>
         <v>30</v>
       </c>
       <c r="J85" s="1">
@@ -3737,17 +4422,17 @@
       </c>
     </row>
     <row r="86" spans="1:10">
-      <c r="A86" s="5">
-        <v>100082</v>
-      </c>
-      <c r="B86" s="5">
-        <v>100082</v>
+      <c r="A86" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="B86" s="5" t="s">
+        <v>287</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>3</v>
@@ -3762,6 +4447,7 @@
         <v>6</v>
       </c>
       <c r="I86" s="1">
+        <f t="shared" si="11"/>
         <v>30</v>
       </c>
       <c r="J86" s="1">
@@ -3769,17 +4455,17 @@
       </c>
     </row>
     <row r="87" spans="1:10">
-      <c r="A87" s="5">
-        <v>100083</v>
-      </c>
-      <c r="B87" s="5">
-        <v>100083</v>
+      <c r="A87" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>288</v>
       </c>
       <c r="C87" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>3</v>
@@ -3794,6 +4480,7 @@
         <v>6</v>
       </c>
       <c r="I87" s="1">
+        <f t="shared" ref="I87:I92" si="12">IF(H87="", "", G87*H87)</f>
         <v>30</v>
       </c>
       <c r="J87" s="1">
@@ -3801,17 +4488,17 @@
       </c>
     </row>
     <row r="88" spans="1:10">
-      <c r="A88" s="5">
-        <v>100084</v>
-      </c>
-      <c r="B88" s="5">
-        <v>100084</v>
+      <c r="A88" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>289</v>
       </c>
       <c r="C88" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>3</v>
@@ -3826,6 +4513,7 @@
         <v>6</v>
       </c>
       <c r="I88" s="1">
+        <f t="shared" si="12"/>
         <v>30</v>
       </c>
       <c r="J88" s="1">
@@ -3833,17 +4521,17 @@
       </c>
     </row>
     <row r="89" spans="1:10">
-      <c r="A89" s="5">
-        <v>100085</v>
-      </c>
-      <c r="B89" s="5">
-        <v>100085</v>
+      <c r="A89" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>290</v>
       </c>
       <c r="C89" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>3</v>
@@ -3858,6 +4546,7 @@
         <v>10</v>
       </c>
       <c r="I89" s="1">
+        <f t="shared" si="12"/>
         <v>30</v>
       </c>
       <c r="J89" s="1">
@@ -3865,17 +4554,17 @@
       </c>
     </row>
     <row r="90" spans="1:10">
-      <c r="A90" s="5">
-        <v>100086</v>
-      </c>
-      <c r="B90" s="5">
-        <v>100086</v>
+      <c r="A90" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>291</v>
       </c>
       <c r="C90" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>3</v>
@@ -3890,6 +4579,7 @@
         <v>12</v>
       </c>
       <c r="I90" s="1">
+        <f t="shared" si="12"/>
         <v>24</v>
       </c>
       <c r="J90" s="1">
@@ -3897,17 +4587,17 @@
       </c>
     </row>
     <row r="91" spans="1:10">
-      <c r="A91" s="5">
-        <v>100087</v>
-      </c>
-      <c r="B91" s="5">
-        <v>100087</v>
+      <c r="A91" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>292</v>
       </c>
       <c r="C91" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>3</v>
@@ -3922,6 +4612,7 @@
         <v>9</v>
       </c>
       <c r="I91" s="1">
+        <f t="shared" si="12"/>
         <v>72</v>
       </c>
       <c r="J91" s="1">
@@ -3929,17 +4620,17 @@
       </c>
     </row>
     <row r="92" spans="1:10">
-      <c r="A92" s="5">
-        <v>100088</v>
-      </c>
-      <c r="B92" s="5">
-        <v>100088</v>
+      <c r="A92" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="B92" s="5" t="s">
+        <v>293</v>
       </c>
       <c r="C92" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>3</v>
@@ -3954,6 +4645,7 @@
         <v>10</v>
       </c>
       <c r="I92" s="1">
+        <f t="shared" si="12"/>
         <v>30</v>
       </c>
       <c r="J92" s="1">
@@ -3961,17 +4653,17 @@
       </c>
     </row>
     <row r="93" spans="1:10">
-      <c r="A93" s="5">
-        <v>100089</v>
-      </c>
-      <c r="B93" s="5">
-        <v>100089</v>
+      <c r="A93" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>294</v>
       </c>
       <c r="C93" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>3</v>
@@ -3986,6 +4678,7 @@
         <v>10</v>
       </c>
       <c r="I93" s="1">
+        <f t="shared" ref="I93:I95" si="13">IF(H93="", "", G93*H93)</f>
         <v>50</v>
       </c>
       <c r="J93" s="1">
@@ -3993,17 +4686,17 @@
       </c>
     </row>
     <row r="94" spans="1:10">
-      <c r="A94" s="5">
-        <v>100090</v>
-      </c>
-      <c r="B94" s="5">
-        <v>100090</v>
+      <c r="A94" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>295</v>
       </c>
       <c r="C94" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>3</v>
@@ -4018,6 +4711,7 @@
         <v>10</v>
       </c>
       <c r="I94" s="1">
+        <f t="shared" si="13"/>
         <v>50</v>
       </c>
       <c r="J94" s="1">
@@ -4025,17 +4719,17 @@
       </c>
     </row>
     <row r="95" spans="1:10">
-      <c r="A95" s="5">
-        <v>100091</v>
-      </c>
-      <c r="B95" s="5">
-        <v>100091</v>
+      <c r="A95" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>296</v>
       </c>
       <c r="C95" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>3</v>
@@ -4050,6 +4744,7 @@
         <v>9</v>
       </c>
       <c r="I95" s="1">
+        <f t="shared" si="13"/>
         <v>36</v>
       </c>
       <c r="J95" s="1">
@@ -4057,17 +4752,17 @@
       </c>
     </row>
     <row r="96" spans="1:10">
-      <c r="A96" s="5">
-        <v>100092</v>
-      </c>
-      <c r="B96" s="5">
-        <v>100092</v>
+      <c r="A96" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="B96" s="5" t="s">
+        <v>297</v>
       </c>
       <c r="C96" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>3</v>
@@ -4082,6 +4777,7 @@
         <v>8</v>
       </c>
       <c r="I96" s="1">
+        <f t="shared" ref="I96:I105" si="14">IF(H96="", "", G96*H96)</f>
         <v>48</v>
       </c>
       <c r="J96" s="1">
@@ -4089,17 +4785,17 @@
       </c>
     </row>
     <row r="97" spans="1:10">
-      <c r="A97" s="5">
-        <v>100093</v>
-      </c>
-      <c r="B97" s="5">
-        <v>100093</v>
+      <c r="A97" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>298</v>
       </c>
       <c r="C97" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>3</v>
@@ -4114,6 +4810,7 @@
         <v>8</v>
       </c>
       <c r="I97" s="1">
+        <f t="shared" si="14"/>
         <v>48</v>
       </c>
       <c r="J97" s="1">
@@ -4121,17 +4818,17 @@
       </c>
     </row>
     <row r="98" spans="1:10">
-      <c r="A98" s="5">
-        <v>100094</v>
-      </c>
-      <c r="B98" s="5">
-        <v>100094</v>
+      <c r="A98" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="B98" s="5" t="s">
+        <v>299</v>
       </c>
       <c r="C98" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>3</v>
@@ -4146,6 +4843,7 @@
         <v>8</v>
       </c>
       <c r="I98" s="1">
+        <f t="shared" si="14"/>
         <v>48</v>
       </c>
       <c r="J98" s="1">
@@ -4153,17 +4851,17 @@
       </c>
     </row>
     <row r="99" spans="1:10">
-      <c r="A99" s="5">
-        <v>100095</v>
-      </c>
-      <c r="B99" s="5">
-        <v>100095</v>
+      <c r="A99" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>300</v>
       </c>
       <c r="C99" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>3</v>
@@ -4178,6 +4876,7 @@
         <v>8</v>
       </c>
       <c r="I99" s="1">
+        <f t="shared" si="14"/>
         <v>48</v>
       </c>
       <c r="J99" s="1">
@@ -4185,17 +4884,17 @@
       </c>
     </row>
     <row r="100" spans="1:10">
-      <c r="A100" s="5">
-        <v>100096</v>
-      </c>
-      <c r="B100" s="5">
-        <v>100096</v>
+      <c r="A100" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="B100" s="5" t="s">
+        <v>301</v>
       </c>
       <c r="C100" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>3</v>
@@ -4210,6 +4909,7 @@
         <v>8</v>
       </c>
       <c r="I100" s="1">
+        <f t="shared" si="14"/>
         <v>48</v>
       </c>
       <c r="J100" s="1">
@@ -4217,17 +4917,17 @@
       </c>
     </row>
     <row r="101" spans="1:10">
-      <c r="A101" s="5">
-        <v>100097</v>
-      </c>
-      <c r="B101" s="5">
-        <v>100097</v>
+      <c r="A101" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>302</v>
       </c>
       <c r="C101" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>3</v>
@@ -4242,6 +4942,7 @@
         <v>8</v>
       </c>
       <c r="I101" s="1">
+        <f t="shared" si="14"/>
         <v>48</v>
       </c>
       <c r="J101" s="1">
@@ -4249,17 +4950,17 @@
       </c>
     </row>
     <row r="102" spans="1:10">
-      <c r="A102" s="5">
-        <v>100098</v>
-      </c>
-      <c r="B102" s="5">
-        <v>100098</v>
+      <c r="A102" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="B102" s="5" t="s">
+        <v>303</v>
       </c>
       <c r="C102" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>3</v>
@@ -4274,6 +4975,7 @@
         <v>8</v>
       </c>
       <c r="I102" s="1">
+        <f t="shared" si="14"/>
         <v>48</v>
       </c>
       <c r="J102" s="1">
@@ -4281,17 +4983,17 @@
       </c>
     </row>
     <row r="103" spans="1:10">
-      <c r="A103" s="5">
-        <v>100099</v>
-      </c>
-      <c r="B103" s="5">
-        <v>100099</v>
+      <c r="A103" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="B103" s="5" t="s">
+        <v>304</v>
       </c>
       <c r="C103" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>3</v>
@@ -4306,6 +5008,7 @@
         <v>8</v>
       </c>
       <c r="I103" s="1">
+        <f t="shared" si="14"/>
         <v>48</v>
       </c>
       <c r="J103" s="1">
@@ -4313,17 +5016,17 @@
       </c>
     </row>
     <row r="104" spans="1:10">
-      <c r="A104" s="5">
-        <v>100100</v>
-      </c>
-      <c r="B104" s="5">
-        <v>100100</v>
+      <c r="A104" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="B104" s="5" t="s">
+        <v>305</v>
       </c>
       <c r="C104" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>3</v>
@@ -4338,6 +5041,7 @@
         <v>8</v>
       </c>
       <c r="I104" s="1">
+        <f t="shared" si="14"/>
         <v>48</v>
       </c>
       <c r="J104" s="1">
@@ -4345,17 +5049,17 @@
       </c>
     </row>
     <row r="105" spans="1:10">
-      <c r="A105" s="5">
-        <v>100101</v>
-      </c>
-      <c r="B105" s="5">
-        <v>100101</v>
+      <c r="A105" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="B105" s="5" t="s">
+        <v>306</v>
       </c>
       <c r="C105" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E105" s="1" t="s">
         <v>3</v>
@@ -4370,6 +5074,7 @@
         <v>8</v>
       </c>
       <c r="I105" s="1">
+        <f t="shared" si="14"/>
         <v>48</v>
       </c>
       <c r="J105" s="1">
@@ -4377,17 +5082,17 @@
       </c>
     </row>
     <row r="106" spans="1:10">
-      <c r="A106" s="5">
-        <v>100102</v>
-      </c>
-      <c r="B106" s="5">
-        <v>100102</v>
+      <c r="A106" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="B106" s="5" t="s">
+        <v>307</v>
       </c>
       <c r="C106" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>3</v>
@@ -4402,24 +5107,25 @@
         <v>8</v>
       </c>
       <c r="I106" s="1">
+        <f t="shared" ref="I106:I108" si="15">IF(H106="", "", G106*H106)</f>
         <v>48</v>
       </c>
       <c r="J106" s="1">
-        <v>4.9800000000000004</v>
+        <v>4.9799999999999995</v>
       </c>
     </row>
     <row r="107" spans="1:10">
-      <c r="A107" s="5">
-        <v>100103</v>
-      </c>
-      <c r="B107" s="5">
-        <v>100103</v>
+      <c r="A107" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="B107" s="5" t="s">
+        <v>308</v>
       </c>
       <c r="C107" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E107" s="1" t="s">
         <v>3</v>
@@ -4434,6 +5140,7 @@
         <v>8</v>
       </c>
       <c r="I107" s="1">
+        <f t="shared" si="15"/>
         <v>48</v>
       </c>
       <c r="J107" s="1">
@@ -4441,17 +5148,17 @@
       </c>
     </row>
     <row r="108" spans="1:10">
-      <c r="A108" s="5">
-        <v>100104</v>
-      </c>
-      <c r="B108" s="5">
-        <v>100104</v>
+      <c r="A108" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="B108" s="5" t="s">
+        <v>309</v>
       </c>
       <c r="C108" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>3</v>
@@ -4466,6 +5173,7 @@
         <v>11</v>
       </c>
       <c r="I108" s="1">
+        <f t="shared" si="15"/>
         <v>55</v>
       </c>
       <c r="J108" s="1">
@@ -4473,17 +5181,17 @@
       </c>
     </row>
     <row r="109" spans="1:10">
-      <c r="A109" s="5">
-        <v>100105</v>
-      </c>
-      <c r="B109" s="5">
-        <v>100105</v>
+      <c r="A109" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="B109" s="5" t="s">
+        <v>310</v>
       </c>
       <c r="C109" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E109" s="1" t="s">
         <v>3</v>
@@ -4498,6 +5206,7 @@
         <v>10</v>
       </c>
       <c r="I109" s="1">
+        <f t="shared" ref="I109:I115" si="16">IF(H109="", "", G109*H109)</f>
         <v>50</v>
       </c>
       <c r="J109" s="1">
@@ -4505,17 +5214,17 @@
       </c>
     </row>
     <row r="110" spans="1:10">
-      <c r="A110" s="5">
-        <v>100106</v>
-      </c>
-      <c r="B110" s="5">
-        <v>100106</v>
+      <c r="A110" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="B110" s="5" t="s">
+        <v>311</v>
       </c>
       <c r="C110" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E110" s="1" t="s">
         <v>3</v>
@@ -4530,6 +5239,7 @@
         <v>10</v>
       </c>
       <c r="I110" s="1">
+        <f t="shared" si="16"/>
         <v>50</v>
       </c>
       <c r="J110" s="1">
@@ -4537,17 +5247,17 @@
       </c>
     </row>
     <row r="111" spans="1:10">
-      <c r="A111" s="5">
-        <v>100107</v>
-      </c>
-      <c r="B111" s="5">
-        <v>100107</v>
+      <c r="A111" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="B111" s="5" t="s">
+        <v>312</v>
       </c>
       <c r="C111" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>3</v>
@@ -4562,6 +5272,7 @@
         <v>10</v>
       </c>
       <c r="I111" s="1">
+        <f t="shared" si="16"/>
         <v>50</v>
       </c>
       <c r="J111" s="1">
@@ -4569,17 +5280,17 @@
       </c>
     </row>
     <row r="112" spans="1:10">
-      <c r="A112" s="5">
-        <v>100108</v>
-      </c>
-      <c r="B112" s="5">
-        <v>100108</v>
+      <c r="A112" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="B112" s="5" t="s">
+        <v>313</v>
       </c>
       <c r="C112" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>3</v>
@@ -4594,6 +5305,7 @@
         <v>10</v>
       </c>
       <c r="I112" s="1">
+        <f t="shared" si="16"/>
         <v>50</v>
       </c>
       <c r="J112" s="1">
@@ -4601,17 +5313,17 @@
       </c>
     </row>
     <row r="113" spans="1:10">
-      <c r="A113" s="5">
-        <v>100109</v>
-      </c>
-      <c r="B113" s="5">
-        <v>100109</v>
+      <c r="A113" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="B113" s="5" t="s">
+        <v>314</v>
       </c>
       <c r="C113" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>3</v>
@@ -4626,6 +5338,7 @@
         <v>9</v>
       </c>
       <c r="I113" s="1">
+        <f t="shared" si="16"/>
         <v>36</v>
       </c>
       <c r="J113" s="1">
@@ -4633,17 +5346,17 @@
       </c>
     </row>
     <row r="114" spans="1:10">
-      <c r="A114" s="5">
-        <v>100110</v>
-      </c>
-      <c r="B114" s="5">
-        <v>100110</v>
+      <c r="A114" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="B114" s="5" t="s">
+        <v>315</v>
       </c>
       <c r="C114" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>3</v>
@@ -4658,6 +5371,7 @@
         <v>10</v>
       </c>
       <c r="I114" s="1">
+        <f t="shared" si="16"/>
         <v>50</v>
       </c>
       <c r="J114" s="1">
@@ -4665,17 +5379,17 @@
       </c>
     </row>
     <row r="115" spans="1:10">
-      <c r="A115" s="5">
-        <v>100111</v>
-      </c>
-      <c r="B115" s="5">
-        <v>100111</v>
+      <c r="A115" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="B115" s="5" t="s">
+        <v>316</v>
       </c>
       <c r="C115" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>3</v>
@@ -4690,6 +5404,7 @@
         <v>9</v>
       </c>
       <c r="I115" s="1">
+        <f t="shared" si="16"/>
         <v>36</v>
       </c>
       <c r="J115" s="1">
@@ -4697,17 +5412,17 @@
       </c>
     </row>
     <row r="116" spans="1:10">
-      <c r="A116" s="5">
-        <v>100112</v>
-      </c>
-      <c r="B116" s="5">
-        <v>100112</v>
+      <c r="A116" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="B116" s="5" t="s">
+        <v>317</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E116" s="1" t="s">
         <v>3</v>
@@ -4722,6 +5437,7 @@
         <v>6</v>
       </c>
       <c r="I116" s="1">
+        <f t="shared" ref="I116:I126" si="17">IF(H116="", "", G116*H116)</f>
         <v>48</v>
       </c>
       <c r="J116" s="1">
@@ -4729,17 +5445,17 @@
       </c>
     </row>
     <row r="117" spans="1:10">
-      <c r="A117" s="5">
-        <v>100113</v>
-      </c>
-      <c r="B117" s="5">
-        <v>100113</v>
+      <c r="A117" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="B117" s="5" t="s">
+        <v>318</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>3</v>
@@ -4754,6 +5470,7 @@
         <v>6</v>
       </c>
       <c r="I117" s="1">
+        <f t="shared" si="17"/>
         <v>48</v>
       </c>
       <c r="J117" s="1">
@@ -4761,17 +5478,17 @@
       </c>
     </row>
     <row r="118" spans="1:10">
-      <c r="A118" s="5">
-        <v>100114</v>
-      </c>
-      <c r="B118" s="5">
-        <v>100114</v>
+      <c r="A118" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="B118" s="5" t="s">
+        <v>319</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E118" s="1" t="s">
         <v>3</v>
@@ -4786,6 +5503,7 @@
         <v>6</v>
       </c>
       <c r="I118" s="1">
+        <f t="shared" si="17"/>
         <v>48</v>
       </c>
       <c r="J118" s="1">
@@ -4793,17 +5511,17 @@
       </c>
     </row>
     <row r="119" spans="1:10">
-      <c r="A119" s="5">
-        <v>100115</v>
-      </c>
-      <c r="B119" s="5">
-        <v>100115</v>
+      <c r="A119" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="B119" s="5" t="s">
+        <v>320</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>3</v>
@@ -4818,6 +5536,7 @@
         <v>6</v>
       </c>
       <c r="I119" s="1">
+        <f t="shared" si="17"/>
         <v>48</v>
       </c>
       <c r="J119" s="1">
@@ -4825,17 +5544,17 @@
       </c>
     </row>
     <row r="120" spans="1:10">
-      <c r="A120" s="5">
-        <v>100116</v>
-      </c>
-      <c r="B120" s="5">
-        <v>100116</v>
+      <c r="A120" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="B120" s="5" t="s">
+        <v>321</v>
       </c>
       <c r="C120" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>3</v>
@@ -4850,6 +5569,7 @@
         <v>6</v>
       </c>
       <c r="I120" s="1">
+        <f t="shared" si="17"/>
         <v>36</v>
       </c>
       <c r="J120" s="1">
@@ -4857,17 +5577,17 @@
       </c>
     </row>
     <row r="121" spans="1:10">
-      <c r="A121" s="5">
-        <v>100117</v>
-      </c>
-      <c r="B121" s="5">
-        <v>100117</v>
+      <c r="A121" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="B121" s="5" t="s">
+        <v>322</v>
       </c>
       <c r="C121" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>3</v>
@@ -4882,6 +5602,7 @@
         <v>9</v>
       </c>
       <c r="I121" s="1">
+        <f t="shared" si="17"/>
         <v>36</v>
       </c>
       <c r="J121" s="1">
@@ -4889,17 +5610,17 @@
       </c>
     </row>
     <row r="122" spans="1:10">
-      <c r="A122" s="5">
-        <v>100118</v>
-      </c>
-      <c r="B122" s="5">
-        <v>100118</v>
+      <c r="A122" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="B122" s="5" t="s">
+        <v>323</v>
       </c>
       <c r="C122" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E122" s="1" t="s">
         <v>3</v>
@@ -4914,6 +5635,7 @@
         <v>9</v>
       </c>
       <c r="I122" s="1">
+        <f t="shared" si="17"/>
         <v>36</v>
       </c>
       <c r="J122" s="1">
@@ -4921,17 +5643,17 @@
       </c>
     </row>
     <row r="123" spans="1:10">
-      <c r="A123" s="5">
-        <v>100119</v>
-      </c>
-      <c r="B123" s="5">
-        <v>100119</v>
+      <c r="A123" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="B123" s="5" t="s">
+        <v>324</v>
       </c>
       <c r="C123" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E123" s="1" t="s">
         <v>3</v>
@@ -4946,6 +5668,7 @@
         <v>6</v>
       </c>
       <c r="I123" s="1">
+        <f t="shared" si="17"/>
         <v>36</v>
       </c>
       <c r="J123" s="1">
@@ -4953,17 +5676,17 @@
       </c>
     </row>
     <row r="124" spans="1:10">
-      <c r="A124" s="5">
-        <v>100120</v>
-      </c>
-      <c r="B124" s="5">
-        <v>100120</v>
+      <c r="A124" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="B124" s="5" t="s">
+        <v>325</v>
       </c>
       <c r="C124" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E124" s="1" t="s">
         <v>3</v>
@@ -4978,6 +5701,7 @@
         <v>6</v>
       </c>
       <c r="I124" s="1">
+        <f t="shared" si="17"/>
         <v>36</v>
       </c>
       <c r="J124" s="1">
@@ -4985,17 +5709,17 @@
       </c>
     </row>
     <row r="125" spans="1:10">
-      <c r="A125" s="5">
-        <v>100121</v>
-      </c>
-      <c r="B125" s="5">
-        <v>100121</v>
+      <c r="A125" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="B125" s="5" t="s">
+        <v>326</v>
       </c>
       <c r="C125" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E125" s="1" t="s">
         <v>3</v>
@@ -5010,6 +5734,7 @@
         <v>6</v>
       </c>
       <c r="I125" s="1">
+        <f t="shared" si="17"/>
         <v>36</v>
       </c>
       <c r="J125" s="1">
@@ -5017,17 +5742,17 @@
       </c>
     </row>
     <row r="126" spans="1:10">
-      <c r="A126" s="5">
-        <v>100122</v>
-      </c>
-      <c r="B126" s="5">
-        <v>100122</v>
+      <c r="A126" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="B126" s="5" t="s">
+        <v>327</v>
       </c>
       <c r="C126" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E126" s="1" t="s">
         <v>3</v>
@@ -5042,6 +5767,7 @@
         <v>6</v>
       </c>
       <c r="I126" s="1">
+        <f t="shared" si="17"/>
         <v>36</v>
       </c>
       <c r="J126" s="1">
@@ -5049,17 +5775,17 @@
       </c>
     </row>
     <row r="127" spans="1:10">
-      <c r="A127" s="5">
-        <v>100123</v>
-      </c>
-      <c r="B127" s="5">
-        <v>100123</v>
+      <c r="A127" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="B127" s="5" t="s">
+        <v>328</v>
       </c>
       <c r="C127" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="E127" s="1" t="s">
         <v>3</v>
@@ -5074,24 +5800,25 @@
         <v>11</v>
       </c>
       <c r="I127" s="1">
+        <f t="shared" ref="I127" si="18">IF(H127="", "", G127*H127)</f>
         <v>55</v>
       </c>
       <c r="J127" s="1">
-        <v>3.35</v>
+        <v>3.3499999999999996</v>
       </c>
     </row>
     <row r="128" spans="1:10">
-      <c r="A128" s="5">
-        <v>100124</v>
-      </c>
-      <c r="B128" s="5">
-        <v>100124</v>
+      <c r="A128" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="B128" s="5" t="s">
+        <v>329</v>
       </c>
       <c r="C128" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="E128" s="1" t="s">
         <v>3</v>
@@ -5106,6 +5833,7 @@
         <v>28</v>
       </c>
       <c r="I128" s="1">
+        <f t="shared" ref="I128:I150" si="19">IF(H128="", "", G128*H128)</f>
         <v>112</v>
       </c>
       <c r="J128" s="1">
@@ -5113,17 +5841,17 @@
       </c>
     </row>
     <row r="129" spans="1:10">
-      <c r="A129" s="5">
-        <v>100125</v>
-      </c>
-      <c r="B129" s="5">
-        <v>100125</v>
+      <c r="A129" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="B129" s="5" t="s">
+        <v>330</v>
       </c>
       <c r="C129" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E129" s="1" t="s">
         <v>3</v>
@@ -5138,6 +5866,7 @@
         <v>11</v>
       </c>
       <c r="I129" s="1">
+        <f t="shared" si="19"/>
         <v>88</v>
       </c>
       <c r="J129" s="1">
@@ -5145,17 +5874,17 @@
       </c>
     </row>
     <row r="130" spans="1:10">
-      <c r="A130" s="5">
-        <v>100126</v>
-      </c>
-      <c r="B130" s="5">
-        <v>100126</v>
+      <c r="A130" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="B130" s="5" t="s">
+        <v>331</v>
       </c>
       <c r="C130" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E130" s="1" t="s">
         <v>3</v>
@@ -5170,6 +5899,7 @@
         <v>11</v>
       </c>
       <c r="I130" s="1">
+        <f t="shared" si="19"/>
         <v>88</v>
       </c>
       <c r="J130" s="1">
@@ -5177,17 +5907,17 @@
       </c>
     </row>
     <row r="131" spans="1:10">
-      <c r="A131" s="5">
-        <v>100127</v>
-      </c>
-      <c r="B131" s="5">
-        <v>100127</v>
+      <c r="A131" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="B131" s="5" t="s">
+        <v>332</v>
       </c>
       <c r="C131" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E131" s="1" t="s">
         <v>3</v>
@@ -5202,6 +5932,7 @@
         <v>12</v>
       </c>
       <c r="I131" s="1">
+        <f t="shared" si="19"/>
         <v>120</v>
       </c>
       <c r="J131" s="1">
@@ -5209,17 +5940,17 @@
       </c>
     </row>
     <row r="132" spans="1:10">
-      <c r="A132" s="5">
-        <v>100128</v>
-      </c>
-      <c r="B132" s="5">
-        <v>100128</v>
+      <c r="A132" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="B132" s="5" t="s">
+        <v>333</v>
       </c>
       <c r="C132" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="E132" s="1" t="s">
         <v>3</v>
@@ -5234,6 +5965,7 @@
         <v>9</v>
       </c>
       <c r="I132" s="1">
+        <f t="shared" si="19"/>
         <v>117</v>
       </c>
       <c r="J132" s="1">
@@ -5241,17 +5973,17 @@
       </c>
     </row>
     <row r="133" spans="1:10">
-      <c r="A133" s="5">
-        <v>100129</v>
-      </c>
-      <c r="B133" s="5">
-        <v>100129</v>
+      <c r="A133" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="B133" s="5" t="s">
+        <v>334</v>
       </c>
       <c r="C133" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="E133" s="1" t="s">
         <v>3</v>
@@ -5266,24 +5998,25 @@
         <v>15</v>
       </c>
       <c r="I133" s="1">
+        <f t="shared" si="19"/>
         <v>120</v>
       </c>
       <c r="J133" s="1">
-        <v>6.98</v>
+        <v>6.9799999999999995</v>
       </c>
     </row>
     <row r="134" spans="1:10">
-      <c r="A134" s="5">
-        <v>100130</v>
-      </c>
-      <c r="B134" s="5">
-        <v>100130</v>
+      <c r="A134" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="B134" s="5" t="s">
+        <v>335</v>
       </c>
       <c r="C134" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="E134" s="1" t="s">
         <v>3</v>
@@ -5298,6 +6031,7 @@
         <v>10</v>
       </c>
       <c r="I134" s="1">
+        <f t="shared" si="19"/>
         <v>60</v>
       </c>
       <c r="J134" s="1">
@@ -5305,17 +6039,17 @@
       </c>
     </row>
     <row r="135" spans="1:10">
-      <c r="A135" s="5">
-        <v>100131</v>
-      </c>
-      <c r="B135" s="5">
-        <v>100131</v>
+      <c r="A135" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="B135" s="5" t="s">
+        <v>336</v>
       </c>
       <c r="C135" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E135" s="1" t="s">
         <v>3</v>
@@ -5330,6 +6064,7 @@
         <v>9</v>
       </c>
       <c r="I135" s="1">
+        <f t="shared" si="19"/>
         <v>117</v>
       </c>
       <c r="J135" s="1">
@@ -5337,17 +6072,17 @@
       </c>
     </row>
     <row r="136" spans="1:10">
-      <c r="A136" s="5">
-        <v>100132</v>
-      </c>
-      <c r="B136" s="5">
-        <v>100132</v>
+      <c r="A136" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="B136" s="5" t="s">
+        <v>337</v>
       </c>
       <c r="C136" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="E136" s="1" t="s">
         <v>3</v>
@@ -5362,6 +6097,7 @@
         <v>9</v>
       </c>
       <c r="I136" s="1">
+        <f t="shared" si="19"/>
         <v>117</v>
       </c>
       <c r="J136" s="1">
@@ -5369,17 +6105,17 @@
       </c>
     </row>
     <row r="137" spans="1:10">
-      <c r="A137" s="5">
-        <v>100133</v>
-      </c>
-      <c r="B137" s="5">
-        <v>100133</v>
+      <c r="A137" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="B137" s="5" t="s">
+        <v>338</v>
       </c>
       <c r="C137" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E137" s="1" t="s">
         <v>3</v>
@@ -5394,6 +6130,7 @@
         <v>28</v>
       </c>
       <c r="I137" s="1">
+        <f t="shared" si="19"/>
         <v>112</v>
       </c>
       <c r="J137" s="1">
@@ -5401,17 +6138,17 @@
       </c>
     </row>
     <row r="138" spans="1:10">
-      <c r="A138" s="5">
-        <v>100134</v>
-      </c>
-      <c r="B138" s="5">
-        <v>100134</v>
+      <c r="A138" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="B138" s="5" t="s">
+        <v>339</v>
       </c>
       <c r="C138" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E138" s="1" t="s">
         <v>3</v>
@@ -5426,6 +6163,7 @@
         <v>9</v>
       </c>
       <c r="I138" s="1">
+        <f t="shared" si="19"/>
         <v>117</v>
       </c>
       <c r="J138" s="1">
@@ -5433,17 +6171,17 @@
       </c>
     </row>
     <row r="139" spans="1:10">
-      <c r="A139" s="5">
-        <v>100135</v>
-      </c>
-      <c r="B139" s="5">
-        <v>100135</v>
+      <c r="A139" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="B139" s="5" t="s">
+        <v>340</v>
       </c>
       <c r="C139" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E139" s="1" t="s">
         <v>3</v>
@@ -5458,6 +6196,7 @@
         <v>9</v>
       </c>
       <c r="I139" s="1">
+        <f t="shared" si="19"/>
         <v>54</v>
       </c>
       <c r="J139" s="1">
@@ -5465,17 +6204,17 @@
       </c>
     </row>
     <row r="140" spans="1:10">
-      <c r="A140" s="5">
-        <v>100136</v>
-      </c>
-      <c r="B140" s="5">
-        <v>100136</v>
+      <c r="A140" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="B140" s="5" t="s">
+        <v>341</v>
       </c>
       <c r="C140" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E140" s="1" t="s">
         <v>3</v>
@@ -5490,6 +6229,7 @@
         <v>6</v>
       </c>
       <c r="I140" s="1">
+        <f t="shared" si="19"/>
         <v>36</v>
       </c>
       <c r="J140" s="1">
@@ -5497,17 +6237,17 @@
       </c>
     </row>
     <row r="141" spans="1:10">
-      <c r="A141" s="5">
-        <v>100137</v>
-      </c>
-      <c r="B141" s="5">
-        <v>100137</v>
+      <c r="A141" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="B141" s="5" t="s">
+        <v>342</v>
       </c>
       <c r="C141" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E141" s="1" t="s">
         <v>3</v>
@@ -5522,6 +6262,7 @@
         <v>9</v>
       </c>
       <c r="I141" s="1">
+        <f t="shared" si="19"/>
         <v>117</v>
       </c>
       <c r="J141" s="1">
@@ -5529,17 +6270,17 @@
       </c>
     </row>
     <row r="142" spans="1:10">
-      <c r="A142" s="5">
-        <v>100138</v>
-      </c>
-      <c r="B142" s="5">
-        <v>100138</v>
+      <c r="A142" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="B142" s="5" t="s">
+        <v>343</v>
       </c>
       <c r="C142" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E142" s="1" t="s">
         <v>3</v>
@@ -5554,6 +6295,7 @@
         <v>9</v>
       </c>
       <c r="I142" s="1">
+        <f t="shared" si="19"/>
         <v>54</v>
       </c>
       <c r="J142" s="1">
@@ -5561,17 +6303,17 @@
       </c>
     </row>
     <row r="143" spans="1:10">
-      <c r="A143" s="5">
-        <v>100139</v>
-      </c>
-      <c r="B143" s="5">
-        <v>100139</v>
+      <c r="A143" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="B143" s="5" t="s">
+        <v>344</v>
       </c>
       <c r="C143" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E143" s="1" t="s">
         <v>3</v>
@@ -5586,6 +6328,7 @@
         <v>15</v>
       </c>
       <c r="I143" s="1">
+        <f t="shared" si="19"/>
         <v>120</v>
       </c>
       <c r="J143" s="1">
@@ -5593,17 +6336,17 @@
       </c>
     </row>
     <row r="144" spans="1:10">
-      <c r="A144" s="5">
-        <v>100140</v>
-      </c>
-      <c r="B144" s="5">
-        <v>100140</v>
+      <c r="A144" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="B144" s="5" t="s">
+        <v>345</v>
       </c>
       <c r="C144" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E144" s="1" t="s">
         <v>3</v>
@@ -5618,6 +6361,7 @@
         <v>10</v>
       </c>
       <c r="I144" s="1">
+        <f t="shared" si="19"/>
         <v>120</v>
       </c>
       <c r="J144" s="1">
@@ -5625,17 +6369,17 @@
       </c>
     </row>
     <row r="145" spans="1:10">
-      <c r="A145" s="5">
-        <v>100141</v>
-      </c>
-      <c r="B145" s="5">
-        <v>100141</v>
+      <c r="A145" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="B145" s="5" t="s">
+        <v>346</v>
       </c>
       <c r="C145" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E145" s="1" t="s">
         <v>3</v>
@@ -5650,6 +6394,7 @@
         <v>10</v>
       </c>
       <c r="I145" s="1">
+        <f t="shared" si="19"/>
         <v>120</v>
       </c>
       <c r="J145" s="1">
@@ -5657,17 +6402,17 @@
       </c>
     </row>
     <row r="146" spans="1:10">
-      <c r="A146" s="5">
-        <v>100142</v>
-      </c>
-      <c r="B146" s="5">
-        <v>100142</v>
+      <c r="A146" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="B146" s="5" t="s">
+        <v>347</v>
       </c>
       <c r="C146" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E146" s="1" t="s">
         <v>3</v>
@@ -5682,6 +6427,7 @@
         <v>28</v>
       </c>
       <c r="I146" s="1">
+        <f t="shared" si="19"/>
         <v>112</v>
       </c>
       <c r="J146" s="1">
@@ -5689,17 +6435,17 @@
       </c>
     </row>
     <row r="147" spans="1:10">
-      <c r="A147" s="5">
-        <v>100143</v>
-      </c>
-      <c r="B147" s="5">
-        <v>100143</v>
+      <c r="A147" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="B147" s="5" t="s">
+        <v>348</v>
       </c>
       <c r="C147" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E147" s="1" t="s">
         <v>3</v>
@@ -5714,6 +6460,7 @@
         <v>9</v>
       </c>
       <c r="I147" s="1">
+        <f t="shared" si="19"/>
         <v>54</v>
       </c>
       <c r="J147" s="1">
@@ -5721,17 +6468,17 @@
       </c>
     </row>
     <row r="148" spans="1:10">
-      <c r="A148" s="5">
-        <v>100144</v>
-      </c>
-      <c r="B148" s="5">
-        <v>100144</v>
+      <c r="A148" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="B148" s="5" t="s">
+        <v>349</v>
       </c>
       <c r="C148" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="E148" s="1" t="s">
         <v>3</v>
@@ -5746,6 +6493,7 @@
         <v>6</v>
       </c>
       <c r="I148" s="1">
+        <f t="shared" si="19"/>
         <v>36</v>
       </c>
       <c r="J148" s="1">
@@ -5753,17 +6501,17 @@
       </c>
     </row>
     <row r="149" spans="1:10">
-      <c r="A149" s="5">
-        <v>100145</v>
-      </c>
-      <c r="B149" s="5">
-        <v>100145</v>
+      <c r="A149" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="B149" s="5" t="s">
+        <v>350</v>
       </c>
       <c r="C149" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E149" s="1" t="s">
         <v>3</v>
@@ -5778,6 +6526,7 @@
         <v>9</v>
       </c>
       <c r="I149" s="1">
+        <f t="shared" si="19"/>
         <v>117</v>
       </c>
       <c r="J149" s="1">
@@ -5785,17 +6534,17 @@
       </c>
     </row>
     <row r="150" spans="1:10">
-      <c r="A150" s="5">
-        <v>100146</v>
-      </c>
-      <c r="B150" s="5">
-        <v>100146</v>
+      <c r="A150" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="B150" s="5" t="s">
+        <v>351</v>
       </c>
       <c r="C150" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E150" s="1" t="s">
         <v>3</v>
@@ -5810,6 +6559,7 @@
         <v>15</v>
       </c>
       <c r="I150" s="1">
+        <f t="shared" si="19"/>
         <v>120</v>
       </c>
       <c r="J150" s="1">
@@ -5817,17 +6567,17 @@
       </c>
     </row>
     <row r="151" spans="1:10">
-      <c r="A151" s="5">
-        <v>100147</v>
-      </c>
-      <c r="B151" s="5">
-        <v>100147</v>
+      <c r="A151" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="B151" s="5" t="s">
+        <v>352</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="E151" s="1" t="s">
         <v>3</v>
@@ -5842,6 +6592,7 @@
         <v>12</v>
       </c>
       <c r="I151" s="1">
+        <f t="shared" ref="I151:I158" si="20">IF(H151="", "", G151*H151)</f>
         <v>60</v>
       </c>
       <c r="J151" s="1">
@@ -5849,17 +6600,17 @@
       </c>
     </row>
     <row r="152" spans="1:10">
-      <c r="A152" s="5">
-        <v>100148</v>
-      </c>
-      <c r="B152" s="5">
-        <v>100148</v>
+      <c r="A152" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="B152" s="5" t="s">
+        <v>353</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="E152" s="1" t="s">
         <v>3</v>
@@ -5874,6 +6625,7 @@
         <v>8</v>
       </c>
       <c r="I152" s="1">
+        <f t="shared" si="20"/>
         <v>48</v>
       </c>
       <c r="J152" s="1">
@@ -5881,17 +6633,17 @@
       </c>
     </row>
     <row r="153" spans="1:10">
-      <c r="A153" s="5">
-        <v>100149</v>
-      </c>
-      <c r="B153" s="5">
-        <v>100149</v>
+      <c r="A153" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="B153" s="5" t="s">
+        <v>354</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E153" s="1" t="s">
         <v>3</v>
@@ -5906,6 +6658,7 @@
         <v>8</v>
       </c>
       <c r="I153" s="1">
+        <f t="shared" si="20"/>
         <v>48</v>
       </c>
       <c r="J153" s="1">
@@ -5913,17 +6666,17 @@
       </c>
     </row>
     <row r="154" spans="1:10">
-      <c r="A154" s="5">
-        <v>100150</v>
-      </c>
-      <c r="B154" s="5">
-        <v>100150</v>
+      <c r="A154" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="B154" s="5" t="s">
+        <v>355</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E154" s="1" t="s">
         <v>3</v>
@@ -5938,6 +6691,7 @@
         <v>8</v>
       </c>
       <c r="I154" s="1">
+        <f t="shared" si="20"/>
         <v>48</v>
       </c>
       <c r="J154" s="1">
@@ -5945,17 +6699,17 @@
       </c>
     </row>
     <row r="155" spans="1:10">
-      <c r="A155" s="5">
-        <v>100151</v>
-      </c>
-      <c r="B155" s="5">
-        <v>100151</v>
+      <c r="A155" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="B155" s="5" t="s">
+        <v>356</v>
       </c>
       <c r="C155" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E155" s="1" t="s">
         <v>3</v>
@@ -5970,6 +6724,7 @@
         <v>10</v>
       </c>
       <c r="I155" s="1">
+        <f t="shared" si="20"/>
         <v>50</v>
       </c>
       <c r="J155" s="1">
@@ -5977,17 +6732,17 @@
       </c>
     </row>
     <row r="156" spans="1:10">
-      <c r="A156" s="5">
-        <v>100152</v>
-      </c>
-      <c r="B156" s="5">
-        <v>100152</v>
+      <c r="A156" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="B156" s="5" t="s">
+        <v>357</v>
       </c>
       <c r="C156" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="E156" s="1" t="s">
         <v>3</v>
@@ -6002,6 +6757,7 @@
         <v>10</v>
       </c>
       <c r="I156" s="1">
+        <f t="shared" si="20"/>
         <v>50</v>
       </c>
       <c r="J156" s="1">
@@ -6009,17 +6765,17 @@
       </c>
     </row>
     <row r="157" spans="1:10">
-      <c r="A157" s="5">
-        <v>100153</v>
-      </c>
-      <c r="B157" s="5">
-        <v>100153</v>
+      <c r="A157" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="B157" s="5" t="s">
+        <v>358</v>
       </c>
       <c r="C157" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="E157" s="1" t="s">
         <v>3</v>
@@ -6034,6 +6790,7 @@
         <v>9</v>
       </c>
       <c r="I157" s="1">
+        <f t="shared" si="20"/>
         <v>36</v>
       </c>
       <c r="J157" s="1">
@@ -6041,17 +6798,17 @@
       </c>
     </row>
     <row r="158" spans="1:10">
-      <c r="A158" s="5">
-        <v>100154</v>
-      </c>
-      <c r="B158" s="5">
-        <v>100154</v>
+      <c r="A158" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="B158" s="5" t="s">
+        <v>359</v>
       </c>
       <c r="C158" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="E158" s="1" t="s">
         <v>3</v>
@@ -6066,24 +6823,25 @@
         <v>9</v>
       </c>
       <c r="I158" s="1">
+        <f t="shared" si="20"/>
         <v>36</v>
       </c>
       <c r="J158" s="1">
-        <v>33.56</v>
+        <v>33.559999999999995</v>
       </c>
     </row>
     <row r="159" spans="1:10">
-      <c r="A159" s="5">
-        <v>100155</v>
-      </c>
-      <c r="B159" s="5">
-        <v>100155</v>
+      <c r="A159" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="B159" s="5" t="s">
+        <v>360</v>
       </c>
       <c r="C159" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="E159" s="1" t="s">
         <v>3</v>
@@ -6098,6 +6856,7 @@
         <v>10</v>
       </c>
       <c r="I159" s="1">
+        <f t="shared" ref="I159:I166" si="21">IF(H159="", "", G159*H159)</f>
         <v>50</v>
       </c>
       <c r="J159" s="1">
@@ -6105,17 +6864,17 @@
       </c>
     </row>
     <row r="160" spans="1:10">
-      <c r="A160" s="5">
-        <v>100156</v>
-      </c>
-      <c r="B160" s="5">
-        <v>100156</v>
+      <c r="A160" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="B160" s="5" t="s">
+        <v>361</v>
       </c>
       <c r="C160" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="E160" s="1" t="s">
         <v>3</v>
@@ -6130,24 +6889,25 @@
         <v>10</v>
       </c>
       <c r="I160" s="1">
+        <f t="shared" si="21"/>
         <v>50</v>
       </c>
       <c r="J160" s="1">
-        <v>12.38</v>
+        <v>12.379999999999999</v>
       </c>
     </row>
     <row r="161" spans="1:10">
-      <c r="A161" s="5">
-        <v>100157</v>
-      </c>
-      <c r="B161" s="5">
-        <v>100157</v>
+      <c r="A161" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="B161" s="5" t="s">
+        <v>362</v>
       </c>
       <c r="C161" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="E161" s="1" t="s">
         <v>3</v>
@@ -6162,24 +6922,25 @@
         <v>9</v>
       </c>
       <c r="I161" s="1">
+        <f t="shared" si="21"/>
         <v>36</v>
       </c>
       <c r="J161" s="1">
-        <v>27.93</v>
+        <v>27.930000000000003</v>
       </c>
     </row>
     <row r="162" spans="1:10">
-      <c r="A162" s="5">
-        <v>100158</v>
-      </c>
-      <c r="B162" s="5">
-        <v>100158</v>
+      <c r="A162" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="B162" s="5" t="s">
+        <v>363</v>
       </c>
       <c r="C162" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E162" s="1" t="s">
         <v>3</v>
@@ -6194,6 +6955,7 @@
         <v>25</v>
       </c>
       <c r="I162" s="1">
+        <f t="shared" si="21"/>
         <v>100</v>
       </c>
       <c r="J162" s="1">
@@ -6201,17 +6963,17 @@
       </c>
     </row>
     <row r="163" spans="1:10">
-      <c r="A163" s="5">
-        <v>100159</v>
-      </c>
-      <c r="B163" s="5">
-        <v>100159</v>
+      <c r="A163" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="B163" s="5" t="s">
+        <v>364</v>
       </c>
       <c r="C163" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="E163" s="1" t="s">
         <v>3</v>
@@ -6226,6 +6988,7 @@
         <v>13</v>
       </c>
       <c r="I163" s="1">
+        <f t="shared" si="21"/>
         <v>91</v>
       </c>
       <c r="J163" s="1">
@@ -6233,17 +6996,17 @@
       </c>
     </row>
     <row r="164" spans="1:10">
-      <c r="A164" s="5">
-        <v>100160</v>
-      </c>
-      <c r="B164" s="5">
-        <v>100160</v>
+      <c r="A164" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="B164" s="5" t="s">
+        <v>365</v>
       </c>
       <c r="C164" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="E164" s="1" t="s">
         <v>3</v>
@@ -6258,6 +7021,7 @@
         <v>12</v>
       </c>
       <c r="I164" s="1">
+        <f t="shared" si="21"/>
         <v>84</v>
       </c>
       <c r="J164" s="1">
@@ -6265,17 +7029,17 @@
       </c>
     </row>
     <row r="165" spans="1:10">
-      <c r="A165" s="5">
-        <v>100161</v>
-      </c>
-      <c r="B165" s="5">
-        <v>100161</v>
+      <c r="A165" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="B165" s="5" t="s">
+        <v>366</v>
       </c>
       <c r="C165" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="E165" s="1" t="s">
         <v>3</v>
@@ -6290,6 +7054,7 @@
         <v>25</v>
       </c>
       <c r="I165" s="1">
+        <f t="shared" si="21"/>
         <v>100</v>
       </c>
       <c r="J165" s="1">
@@ -6297,17 +7062,17 @@
       </c>
     </row>
     <row r="166" spans="1:10">
-      <c r="A166" s="5">
-        <v>100162</v>
-      </c>
-      <c r="B166" s="5">
-        <v>100162</v>
+      <c r="A166" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="B166" s="5" t="s">
+        <v>367</v>
       </c>
       <c r="C166" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E166" s="1" t="s">
         <v>3</v>
@@ -6322,6 +7087,7 @@
         <v>10</v>
       </c>
       <c r="I166" s="1">
+        <f t="shared" si="21"/>
         <v>50</v>
       </c>
       <c r="J166" s="1">
@@ -6329,17 +7095,17 @@
       </c>
     </row>
     <row r="167" spans="1:10">
-      <c r="A167" s="5">
-        <v>100163</v>
-      </c>
-      <c r="B167" s="5">
-        <v>100163</v>
+      <c r="A167" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="B167" s="5" t="s">
+        <v>368</v>
       </c>
       <c r="C167" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E167" s="1" t="s">
         <v>3</v>
@@ -6354,6 +7120,7 @@
         <v>6</v>
       </c>
       <c r="I167" s="1">
+        <f t="shared" ref="I167:I169" si="22">IF(H167="", "", G167*H167)</f>
         <v>42</v>
       </c>
       <c r="J167" s="1">
@@ -6361,17 +7128,17 @@
       </c>
     </row>
     <row r="168" spans="1:10">
-      <c r="A168" s="5">
-        <v>100164</v>
-      </c>
-      <c r="B168" s="5">
-        <v>100164</v>
+      <c r="A168" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="B168" s="5" t="s">
+        <v>369</v>
       </c>
       <c r="C168" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E168" s="1" t="s">
         <v>3</v>
@@ -6386,6 +7153,7 @@
         <v>6</v>
       </c>
       <c r="I168" s="1">
+        <f t="shared" si="22"/>
         <v>42</v>
       </c>
       <c r="J168" s="1">
@@ -6393,17 +7161,17 @@
       </c>
     </row>
     <row r="169" spans="1:10">
-      <c r="A169" s="5">
-        <v>100165</v>
-      </c>
-      <c r="B169" s="5">
-        <v>100165</v>
+      <c r="A169" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="B169" s="5" t="s">
+        <v>370</v>
       </c>
       <c r="C169" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="E169" s="1" t="s">
         <v>3</v>
@@ -6418,6 +7186,7 @@
         <v>6</v>
       </c>
       <c r="I169" s="1">
+        <f t="shared" si="22"/>
         <v>42</v>
       </c>
       <c r="J169" s="1">
@@ -6425,17 +7194,17 @@
       </c>
     </row>
     <row r="170" spans="1:10">
-      <c r="A170" s="5">
-        <v>100166</v>
-      </c>
-      <c r="B170" s="5">
-        <v>100166</v>
+      <c r="A170" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="B170" s="5" t="s">
+        <v>371</v>
       </c>
       <c r="C170" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E170" s="1" t="s">
         <v>3</v>
@@ -6450,6 +7219,7 @@
         <v>11</v>
       </c>
       <c r="I170" s="1">
+        <f t="shared" ref="I170:I178" si="23">IF(H170="", "", G170*H170)</f>
         <v>55</v>
       </c>
       <c r="J170" s="1">
@@ -6457,17 +7227,17 @@
       </c>
     </row>
     <row r="171" spans="1:10">
-      <c r="A171" s="5">
-        <v>100167</v>
-      </c>
-      <c r="B171" s="5">
-        <v>100167</v>
+      <c r="A171" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="B171" s="5" t="s">
+        <v>372</v>
       </c>
       <c r="C171" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E171" s="1" t="s">
         <v>3</v>
@@ -6482,6 +7252,7 @@
         <v>11</v>
       </c>
       <c r="I171" s="1">
+        <f t="shared" si="23"/>
         <v>55</v>
       </c>
       <c r="J171" s="1">
@@ -6489,17 +7260,17 @@
       </c>
     </row>
     <row r="172" spans="1:10">
-      <c r="A172" s="5">
-        <v>100168</v>
-      </c>
-      <c r="B172" s="5">
-        <v>100168</v>
+      <c r="A172" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="B172" s="5" t="s">
+        <v>373</v>
       </c>
       <c r="C172" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E172" s="1" t="s">
         <v>3</v>
@@ -6514,6 +7285,7 @@
         <v>10</v>
       </c>
       <c r="I172" s="1">
+        <f t="shared" si="23"/>
         <v>70</v>
       </c>
       <c r="J172" s="1">
@@ -6521,17 +7293,17 @@
       </c>
     </row>
     <row r="173" spans="1:10">
-      <c r="A173" s="5">
-        <v>100169</v>
-      </c>
-      <c r="B173" s="5">
-        <v>100169</v>
+      <c r="A173" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="B173" s="5" t="s">
+        <v>374</v>
       </c>
       <c r="C173" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E173" s="1" t="s">
         <v>3</v>
@@ -6546,6 +7318,7 @@
         <v>11</v>
       </c>
       <c r="I173" s="1">
+        <f t="shared" si="23"/>
         <v>44</v>
       </c>
       <c r="J173" s="1">
@@ -6553,17 +7326,17 @@
       </c>
     </row>
     <row r="174" spans="1:10">
-      <c r="A174" s="5">
-        <v>100170</v>
-      </c>
-      <c r="B174" s="5">
-        <v>100170</v>
+      <c r="A174" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="B174" s="5" t="s">
+        <v>375</v>
       </c>
       <c r="C174" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="E174" s="1" t="s">
         <v>3</v>
@@ -6578,6 +7351,7 @@
         <v>11</v>
       </c>
       <c r="I174" s="1">
+        <f t="shared" si="23"/>
         <v>44</v>
       </c>
       <c r="J174" s="1">
@@ -6585,17 +7359,17 @@
       </c>
     </row>
     <row r="175" spans="1:10">
-      <c r="A175" s="5">
-        <v>100171</v>
-      </c>
-      <c r="B175" s="5">
-        <v>100171</v>
+      <c r="A175" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="B175" s="5" t="s">
+        <v>376</v>
       </c>
       <c r="C175" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E175" s="1" t="s">
         <v>3</v>
@@ -6610,6 +7384,7 @@
         <v>11</v>
       </c>
       <c r="I175" s="1">
+        <f t="shared" si="23"/>
         <v>44</v>
       </c>
       <c r="J175" s="1">
@@ -6617,17 +7392,17 @@
       </c>
     </row>
     <row r="176" spans="1:10">
-      <c r="A176" s="5">
-        <v>100172</v>
-      </c>
-      <c r="B176" s="5">
-        <v>100172</v>
+      <c r="A176" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="B176" s="5" t="s">
+        <v>377</v>
       </c>
       <c r="C176" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E176" s="1" t="s">
         <v>3</v>
@@ -6642,6 +7417,7 @@
         <v>11</v>
       </c>
       <c r="I176" s="1">
+        <f t="shared" si="23"/>
         <v>55</v>
       </c>
       <c r="J176" s="1">
@@ -6649,17 +7425,17 @@
       </c>
     </row>
     <row r="177" spans="1:10">
-      <c r="A177" s="5">
-        <v>100173</v>
-      </c>
-      <c r="B177" s="5">
-        <v>100173</v>
+      <c r="A177" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B177" s="5" t="s">
+        <v>18</v>
       </c>
       <c r="C177" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="E177" s="1" t="s">
         <v>3</v>
@@ -6674,6 +7450,7 @@
         <v>21</v>
       </c>
       <c r="I177" s="1">
+        <f t="shared" si="23"/>
         <v>84</v>
       </c>
       <c r="J177" s="1">
@@ -6681,17 +7458,17 @@
       </c>
     </row>
     <row r="178" spans="1:10">
-      <c r="A178" s="5">
-        <v>100173</v>
-      </c>
-      <c r="B178" s="5">
-        <v>200173</v>
+      <c r="A178" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B178" s="5" t="s">
+        <v>393</v>
       </c>
       <c r="C178" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="E178" s="1" t="s">
         <v>4</v>
@@ -6706,6 +7483,7 @@
         <v>21</v>
       </c>
       <c r="I178" s="1">
+        <f t="shared" si="23"/>
         <v>84</v>
       </c>
       <c r="J178" s="1">
@@ -6713,17 +7491,17 @@
       </c>
     </row>
     <row r="179" spans="1:10">
-      <c r="A179" s="5">
-        <v>100174</v>
-      </c>
-      <c r="B179" s="5">
-        <v>100174</v>
+      <c r="A179" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="B179" s="5" t="s">
+        <v>378</v>
       </c>
       <c r="C179" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="E179" s="1" t="s">
         <v>3</v>
@@ -6738,6 +7516,7 @@
         <v>9</v>
       </c>
       <c r="I179" s="1">
+        <f t="shared" ref="I179:I181" si="24">IF(H179="", "", G179*H179)</f>
         <v>27</v>
       </c>
       <c r="J179" s="1">
@@ -6745,17 +7524,17 @@
       </c>
     </row>
     <row r="180" spans="1:10">
-      <c r="A180" s="5">
-        <v>100175</v>
-      </c>
-      <c r="B180" s="5">
-        <v>100175</v>
+      <c r="A180" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="B180" s="5" t="s">
+        <v>379</v>
       </c>
       <c r="C180" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="E180" s="1" t="s">
         <v>3</v>
@@ -6770,6 +7549,7 @@
         <v>10</v>
       </c>
       <c r="I180" s="1">
+        <f t="shared" si="24"/>
         <v>80</v>
       </c>
       <c r="J180" s="1">
@@ -6777,17 +7557,17 @@
       </c>
     </row>
     <row r="181" spans="1:10">
-      <c r="A181" s="5">
-        <v>100176</v>
-      </c>
-      <c r="B181" s="5">
-        <v>100176</v>
+      <c r="A181" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="B181" s="5" t="s">
+        <v>380</v>
       </c>
       <c r="C181" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="E181" s="1" t="s">
         <v>3</v>
@@ -6802,6 +7582,7 @@
         <v>6</v>
       </c>
       <c r="I181" s="1">
+        <f t="shared" si="24"/>
         <v>24</v>
       </c>
       <c r="J181" s="1">
@@ -6809,17 +7590,17 @@
       </c>
     </row>
     <row r="182" spans="1:10">
-      <c r="A182" s="5">
-        <v>100177</v>
-      </c>
-      <c r="B182" s="5">
-        <v>100177</v>
+      <c r="A182" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="B182" s="5" t="s">
+        <v>381</v>
       </c>
       <c r="C182" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="E182" s="1" t="s">
         <v>3</v>
@@ -6834,6 +7615,7 @@
         <v>13</v>
       </c>
       <c r="I182" s="1">
+        <f t="shared" ref="I182:I187" si="25">IF(H182="", "", G182*H182)</f>
         <v>78</v>
       </c>
       <c r="J182" s="1">
@@ -6841,17 +7623,17 @@
       </c>
     </row>
     <row r="183" spans="1:10">
-      <c r="A183" s="5">
-        <v>100178</v>
-      </c>
-      <c r="B183" s="5">
-        <v>100178</v>
+      <c r="A183" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="B183" s="5" t="s">
+        <v>382</v>
       </c>
       <c r="C183" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="E183" s="1" t="s">
         <v>3</v>
@@ -6866,6 +7648,7 @@
         <v>11</v>
       </c>
       <c r="I183" s="1">
+        <f t="shared" si="25"/>
         <v>77</v>
       </c>
       <c r="J183" s="1">
@@ -6873,17 +7656,17 @@
       </c>
     </row>
     <row r="184" spans="1:10">
-      <c r="A184" s="5">
-        <v>100179</v>
-      </c>
-      <c r="B184" s="5">
-        <v>100179</v>
+      <c r="A184" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="B184" s="5" t="s">
+        <v>383</v>
       </c>
       <c r="C184" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="E184" s="1" t="s">
         <v>3</v>
@@ -6898,6 +7681,7 @@
         <v>13</v>
       </c>
       <c r="I184" s="1">
+        <f t="shared" si="25"/>
         <v>78</v>
       </c>
       <c r="J184" s="1">
@@ -6905,17 +7689,17 @@
       </c>
     </row>
     <row r="185" spans="1:10">
-      <c r="A185" s="5">
-        <v>100180</v>
-      </c>
-      <c r="B185" s="5">
-        <v>100180</v>
+      <c r="A185" s="5" t="s">
+        <v>384</v>
+      </c>
+      <c r="B185" s="5" t="s">
+        <v>384</v>
       </c>
       <c r="C185" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="E185" s="1" t="s">
         <v>3</v>
@@ -6930,6 +7714,7 @@
         <v>11</v>
       </c>
       <c r="I185" s="1">
+        <f t="shared" si="25"/>
         <v>55</v>
       </c>
       <c r="J185" s="1">
@@ -6937,17 +7722,17 @@
       </c>
     </row>
     <row r="186" spans="1:10">
-      <c r="A186" s="5">
-        <v>100181</v>
-      </c>
-      <c r="B186" s="5">
-        <v>100181</v>
+      <c r="A186" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="B186" s="5" t="s">
+        <v>385</v>
       </c>
       <c r="C186" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="E186" s="1" t="s">
         <v>3</v>
@@ -6962,6 +7747,7 @@
         <v>7</v>
       </c>
       <c r="I186" s="1">
+        <f t="shared" si="25"/>
         <v>84</v>
       </c>
       <c r="J186" s="1">
@@ -6969,17 +7755,17 @@
       </c>
     </row>
     <row r="187" spans="1:10">
-      <c r="A187" s="5">
-        <v>100182</v>
-      </c>
-      <c r="B187" s="5">
-        <v>100182</v>
+      <c r="A187" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="B187" s="5" t="s">
+        <v>386</v>
       </c>
       <c r="C187" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="E187" s="1" t="s">
         <v>3</v>
@@ -6994,6 +7780,7 @@
         <v>7</v>
       </c>
       <c r="I187" s="1">
+        <f t="shared" si="25"/>
         <v>84</v>
       </c>
       <c r="J187" s="1">
@@ -7001,17 +7788,17 @@
       </c>
     </row>
     <row r="188" spans="1:10">
-      <c r="A188" s="5">
-        <v>100183</v>
-      </c>
-      <c r="B188" s="5">
-        <v>100183</v>
+      <c r="A188" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="B188" s="5" t="s">
+        <v>387</v>
       </c>
       <c r="C188" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="E188" s="1" t="s">
         <v>3</v>
@@ -7026,6 +7813,7 @@
         <v>10</v>
       </c>
       <c r="I188" s="1">
+        <f t="shared" ref="I188:I190" si="26">IF(H188="", "", G188*H188)</f>
         <v>50</v>
       </c>
       <c r="J188" s="1">
@@ -7033,17 +7821,17 @@
       </c>
     </row>
     <row r="189" spans="1:10">
-      <c r="A189" s="5">
-        <v>100184</v>
-      </c>
-      <c r="B189" s="5">
-        <v>100184</v>
+      <c r="A189" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="B189" s="5" t="s">
+        <v>388</v>
       </c>
       <c r="C189" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E189" s="1" t="s">
         <v>3</v>
@@ -7058,6 +7846,7 @@
         <v>10</v>
       </c>
       <c r="I189" s="1">
+        <f t="shared" si="26"/>
         <v>50</v>
       </c>
       <c r="J189" s="1">
@@ -7065,17 +7854,17 @@
       </c>
     </row>
     <row r="190" spans="1:10">
-      <c r="A190" s="5">
-        <v>100185</v>
-      </c>
-      <c r="B190" s="5">
-        <v>100185</v>
+      <c r="A190" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="B190" s="5" t="s">
+        <v>389</v>
       </c>
       <c r="C190" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="E190" s="1" t="s">
         <v>3</v>
@@ -7090,10 +7879,11 @@
         <v>9</v>
       </c>
       <c r="I190" s="1">
+        <f t="shared" si="26"/>
         <v>36</v>
       </c>
       <c r="J190" s="1">
-        <v>29.36</v>
+        <v>29.360000000000003</v>
       </c>
     </row>
     <row r="191" spans="1:10">
